--- a/outputs/q3/结果提交_Q3.xlsx
+++ b/outputs/q3/结果提交_Q3.xlsx
@@ -1527,11 +1527,11 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>R-COMP-01</t>
+          <t>R-COMP-06</t>
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>81.00344048954707</v>
+        <v>62.53744048954707</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>109.2038334</v>
@@ -1543,16 +1543,16 @@
         <v>827.4551391601562</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>810.979</v>
+        <v>792.5129999999999</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>1925.918</v>
+        <v>1925.668</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>2504.206487773799</v>
+        <v>2503.956487773799</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.6324982830709728</v>
+        <v>0.6380642830709727</v>
       </c>
       <c r="L2" s="3" t="n"/>
       <c r="M2" s="3" t="n"/>
@@ -1571,11 +1571,11 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>R-COMP-02</t>
+          <t>R-COMP-05</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>109.8448991956604</v>
+        <v>107.0018991956604</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>109.279931</v>
@@ -1587,16 +1587,16 @@
         <v>702.4266357421875</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>840.2</v>
+        <v>837.357</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>3604.149</v>
+        <v>3556.62</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>4172.397987116188</v>
+        <v>4124.868987116189</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>1.145458405613868</v>
+        <v>1.131804350058313</v>
       </c>
       <c r="L3" s="3" t="n"/>
       <c r="M3" s="3" t="n"/>
@@ -1619,28 +1619,28 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>2882.501177057822</v>
+        <v>2803.957373689164</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>109.2363506</v>
+        <v>109.2389554</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>23.05923958644987</v>
+        <v>23.0642504</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>628.6170654296875</v>
+        <v>597.3832702636719</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>3594.149</v>
+        <v>3546.619999999999</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>5178.351</v>
+        <v>5539.141</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>5721.741911727985</v>
+        <v>6110.943898832808</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.7782548590614248</v>
+        <v>0.9250457269198947</v>
       </c>
       <c r="L4" s="3" t="n"/>
       <c r="M4" s="3" t="n"/>
@@ -1663,7 +1663,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>4479.752893111123</v>
+        <v>4513.587893111123</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>109.2052968146341</v>
@@ -1675,61 +1675,33 @@
         <v>717.0950012207031</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>5168.351</v>
+        <v>5202.186</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>6787.068</v>
+        <v>6447.53</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>7314.782356990602</v>
+        <v>6975.244356990602</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.7678096354118646</v>
+        <v>0.65372344096742</v>
       </c>
       <c r="L5" s="3" t="n"/>
       <c r="M5" s="3" t="n"/>
       <c r="N5" s="3" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Q3-R05</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>R-COMP-05</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>6145.052240382385</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>109.2213944</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>23.0371501</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>515.1659545898438</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>6673.026999999999</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>6970.845</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>7321.108589166768</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0.2758800591476346</v>
-      </c>
+      <c r="A6" s="3" t="n"/>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="n"/>
       <c r="L6" s="3" t="n"/>
       <c r="M6" s="3" t="n"/>
       <c r="N6" s="3" t="n"/>
@@ -2113,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W287"/>
+  <dimension ref="A1:W273"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="14" customWidth="1" style="8" min="1" max="2"/>
@@ -2183,10 +2155,10 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>362.716</v>
+        <v>360</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>517.4651292317708</v>
+        <v>439.4659464518229</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
@@ -2224,10 +2196,10 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>517.4651292317708</v>
+        <v>439.4659464518229</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>845.0681146428053</v>
+        <v>704.9832946529609</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
@@ -2261,25 +2233,21 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>leg1:cruise</t>
+          <t>leg1:descent</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>845.0681146428053</v>
+        <v>704.9832946529609</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>969.0986174161992</v>
+        <v>725.5024303951484</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n"/>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="3" t="n"/>
@@ -2306,25 +2274,21 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>leg1:descent</t>
+          <t>S006:handover</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>969.0986174161992</v>
+        <v>725.5024303951484</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1065.477572494324</v>
+        <v>935.5024303951484</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
@@ -2351,25 +2315,21 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>S014:handover</t>
+          <t>leg2:climb</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1065.477572494324</v>
+        <v>935.5024303951484</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1275.477572494324</v>
+        <v>952.6017101803046</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n"/>
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="3" t="n"/>
       <c r="I6" s="3" t="n"/>
@@ -2396,25 +2356,21 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>leg2:climb</t>
+          <t>leg2:cruise</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1275.477572494324</v>
+        <v>952.6017101803046</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1355.793368392762</v>
+        <v>1218.119058381443</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n"/>
       <c r="G7" s="3" t="n"/>
       <c r="H7" s="3" t="n"/>
       <c r="I7" s="3" t="n"/>
@@ -2441,25 +2397,21 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>leg2:cruise</t>
+          <t>leg2:descent</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1355.793368392762</v>
+        <v>1218.119058381443</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1479.823871166156</v>
+        <v>1313.47819412363</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n"/>
       <c r="G8" s="3" t="n"/>
       <c r="H8" s="3" t="n"/>
       <c r="I8" s="3" t="n"/>
@@ -2481,19 +2433,19 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Q2-001</t>
+          <t>Q2-002</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>leg2:cruise</t>
+          <t>leg1:climb</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1479.823871166156</v>
+        <v>1983.052</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1807.42685657719</v>
+        <v>2062.517946451823</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
@@ -2522,19 +2474,19 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Q2-001</t>
+          <t>Q2-002</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>leg2:descent</t>
+          <t>leg1:cruise</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1807.42685657719</v>
+        <v>2062.517946451823</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1993.125811655315</v>
+        <v>2274.931825012733</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
@@ -2568,14 +2520,14 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>leg1:climb</t>
+          <t>leg1:descent</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2667.287</v>
+        <v>2274.931825012733</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2727.705084716797</v>
+        <v>2295.450960754921</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
@@ -2609,14 +2561,14 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>leg1:cruise</t>
+          <t>S006:handover</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2727.705084716797</v>
+        <v>2295.450960754921</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>3057.129986234433</v>
+        <v>2505.450960754921</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
@@ -2650,25 +2602,21 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>leg1:cruise</t>
+          <t>leg2:climb</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>3057.129986234433</v>
+        <v>2505.450960754921</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>3345.314289307145</v>
+        <v>2522.550240540077</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n"/>
       <c r="G13" s="3" t="n"/>
       <c r="H13" s="3" t="n"/>
       <c r="I13" s="3" t="n"/>
@@ -2695,25 +2643,21 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>leg1:descent</t>
+          <t>leg2:cruise</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>3345.314289307145</v>
+        <v>2522.550240540077</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3381.095990967302</v>
+        <v>2734.964119100987</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="n"/>
       <c r="G14" s="3" t="n"/>
       <c r="H14" s="3" t="n"/>
       <c r="I14" s="3" t="n"/>
@@ -2740,25 +2684,21 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>S002:handover</t>
+          <t>leg2:descent</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>3381.095990967302</v>
+        <v>2734.964119100987</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3561.095990967302</v>
+        <v>2830.323254843175</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="n"/>
       <c r="G15" s="3" t="n"/>
       <c r="H15" s="3" t="n"/>
       <c r="I15" s="3" t="n"/>
@@ -2780,30 +2720,26 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Q2-002</t>
+          <t>Q2-003</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>leg2:climb</t>
+          <t>leg1:climb</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>3561.095990967302</v>
+        <v>5259.153</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>3594.149</v>
+        <v>5340.889444091797</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="n"/>
       <c r="G16" s="3" t="n"/>
       <c r="H16" s="3" t="n"/>
       <c r="I16" s="3" t="n"/>
@@ -2825,30 +2761,26 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Q2-002</t>
+          <t>Q2-003</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>leg2:climb</t>
+          <t>leg1:cruise</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>3594.149</v>
+        <v>5340.889444091797</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>3599.148725342302</v>
+        <v>5631.24726987239</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R03</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n"/>
       <c r="G17" s="3" t="n"/>
       <c r="H17" s="3" t="n"/>
       <c r="I17" s="3" t="n"/>
@@ -2870,19 +2802,19 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Q2-002</t>
+          <t>Q2-003</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>leg2:cruise</t>
+          <t>leg1:cruise</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>3599.148725342302</v>
+        <v>5631.24726987239</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3786.483533524521</v>
+        <v>5879.491651586677</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
@@ -2891,7 +2823,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Q3-R03</t>
+          <t>Q3-R04</t>
         </is>
       </c>
       <c r="G18" s="3" t="n"/>
@@ -2915,19 +2847,19 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Q2-002</t>
+          <t>Q2-003</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>leg2:descent</t>
+          <t>leg1:descent</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>3786.483533524521</v>
+        <v>5879.491651586677</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>3828.626814774521</v>
+        <v>5920.295384496833</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
@@ -2936,7 +2868,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Q3-R03</t>
+          <t>Q3-R04</t>
         </is>
       </c>
       <c r="G19" s="3" t="n"/>
@@ -2960,19 +2892,19 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Q2-002</t>
+          <t>Q2-003</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>S004:handover</t>
+          <t>S008:handover</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>3828.626814774521</v>
+        <v>5920.295384496833</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>4038.626814774521</v>
+        <v>6160.295384496833</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -2981,7 +2913,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Q3-R03</t>
+          <t>Q3-R04</t>
         </is>
       </c>
       <c r="G20" s="3" t="n"/>
@@ -3005,19 +2937,19 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Q2-002</t>
+          <t>Q2-003</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>leg3:climb</t>
+          <t>leg2:climb</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>4038.626814774521</v>
+        <v>6160.295384496833</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>4095.273203527776</v>
+        <v>6194.298495255297</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
@@ -3026,7 +2958,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Q3-R03</t>
+          <t>Q3-R04</t>
         </is>
       </c>
       <c r="G21" s="3" t="n"/>
@@ -3050,19 +2982,19 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Q2-002</t>
+          <t>Q2-003</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>leg3:cruise</t>
+          <t>leg2:cruise</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>4095.273203527776</v>
+        <v>6194.298495255297</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>4272.68072701018</v>
+        <v>6442.542876969584</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
@@ -3071,7 +3003,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Q3-R03</t>
+          <t>Q3-R04</t>
         </is>
       </c>
       <c r="G22" s="3" t="n"/>
@@ -3095,19 +3027,19 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Q2-002</t>
+          <t>Q2-003</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>leg3:cruise</t>
+          <t>leg2:cruise</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>4272.68072701018</v>
+        <v>6442.542876969584</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>4738.164574287541</v>
+        <v>6732.900702750176</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
@@ -3136,19 +3068,19 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Q2-002</t>
+          <t>Q2-003</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>leg3:descent</t>
+          <t>leg2:descent</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>4738.164574287541</v>
+        <v>6732.900702750176</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4846.380240791447</v>
+        <v>6830.984435660332</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
@@ -3177,7 +3109,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Q2-003</t>
+          <t>Q2-004</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -3186,10 +3118,10 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1703.479</v>
+        <v>5509.607</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1858.228129231771</v>
+        <v>5564.783304117838</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
@@ -3218,7 +3150,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Q2-003</t>
+          <t>Q2-004</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -3227,10 +3159,10 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1858.228129231771</v>
+        <v>5564.783304117838</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>2185.831114642806</v>
+        <v>5894.233928911088</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
@@ -3259,7 +3191,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Q2-003</t>
+          <t>Q2-004</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -3268,10 +3200,10 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2185.831114642806</v>
+        <v>5894.233928911088</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2309.861617416199</v>
+        <v>6040.212050974258</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
@@ -3280,7 +3212,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R04</t>
         </is>
       </c>
       <c r="G27" s="3" t="n"/>
@@ -3304,7 +3236,7 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Q2-003</t>
+          <t>Q2-004</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -3313,10 +3245,10 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2309.861617416199</v>
+        <v>6040.212050974258</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>2406.240572494324</v>
+        <v>6065.503615915664</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
@@ -3325,7 +3257,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R04</t>
         </is>
       </c>
       <c r="G28" s="3" t="n"/>
@@ -3349,19 +3281,19 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Q2-003</t>
+          <t>Q2-004</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>S014:handover</t>
+          <t>S009:handover</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2406.240572494324</v>
+        <v>6065.503615915664</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2586.240572494324</v>
+        <v>6275.503615915664</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
@@ -3370,7 +3302,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R04</t>
         </is>
       </c>
       <c r="G29" s="3" t="n"/>
@@ -3394,7 +3326,7 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Q2-003</t>
+          <t>Q2-004</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -3403,10 +3335,10 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2586.240572494324</v>
+        <v>6275.503615915664</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>2675.429516993022</v>
+        <v>6296.579920033503</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
@@ -3415,7 +3347,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R04</t>
         </is>
       </c>
       <c r="G30" s="3" t="n"/>
@@ -3439,7 +3371,7 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Q2-003</t>
+          <t>Q2-004</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -3448,10 +3380,10 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2675.429516993022</v>
+        <v>6296.579920033503</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2812.049132622352</v>
+        <v>6442.558042096673</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
@@ -3460,7 +3392,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R04</t>
         </is>
       </c>
       <c r="G31" s="3" t="n"/>
@@ -3484,7 +3416,7 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Q2-003</t>
+          <t>Q2-004</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -3493,10 +3425,10 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2812.049132622352</v>
+        <v>6442.558042096673</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>3269.406107542496</v>
+        <v>6772.008666889923</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
@@ -3525,7 +3457,7 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Q2-003</t>
+          <t>Q2-004</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -3534,10 +3466,10 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>3269.406107542496</v>
+        <v>6772.008666889923</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>3431.992840940934</v>
+        <v>6838.220231831329</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
@@ -3566,19 +3498,19 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Q2-003</t>
+          <t>Q2-005</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>S011:handover</t>
+          <t>leg1:climb</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>3431.992840940934</v>
+        <v>510</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>3641.992840940934</v>
+        <v>568.1426440429688</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
@@ -3607,19 +3539,19 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Q2-003</t>
+          <t>Q2-005</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>leg3:climb</t>
+          <t>leg1:cruise</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>3641.992840940934</v>
+        <v>568.1426440429688</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>3669.746759397965</v>
+        <v>771.7412336108687</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
@@ -3648,19 +3580,19 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Q2-003</t>
+          <t>Q2-005</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>leg3:cruise</t>
+          <t>leg1:descent</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>3669.746759397965</v>
+        <v>771.7412336108687</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>3903.752945454769</v>
+        <v>816.2695386645796</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
@@ -3689,19 +3621,19 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Q2-003</t>
+          <t>Q2-005</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>leg3:descent</t>
+          <t>S001:handover</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>3903.752945454769</v>
+        <v>816.2695386645796</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>3970.817647603206</v>
+        <v>1248.26953866458</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
@@ -3730,19 +3662,19 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Q2-004</t>
+          <t>Q2-005</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>leg1:climb</t>
+          <t>leg2:climb</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>2353.126</v>
+        <v>1248.26953866458</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>2443.61994124349</v>
+        <v>1283.892182707548</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
@@ -3771,19 +3703,19 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Q2-004</t>
+          <t>Q2-005</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>leg1:cruise</t>
+          <t>leg2:cruise</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>2443.61994124349</v>
+        <v>1283.892182707548</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>2772.625692100219</v>
+        <v>1487.490772275448</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
@@ -3812,30 +3744,26 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Q2-004</t>
+          <t>Q2-005</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>leg1:cruise</t>
+          <t>leg2:descent</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>2772.625692100219</v>
+        <v>1487.490772275448</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>2847.723472679366</v>
+        <v>1560.169077329159</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="n"/>
       <c r="G40" s="3" t="n"/>
       <c r="H40" s="3" t="n"/>
       <c r="I40" s="3" t="n"/>
@@ -3857,30 +3785,26 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Q2-004</t>
+          <t>Q2-006</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>leg1:descent</t>
+          <t>leg1:climb</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>2847.723472679366</v>
+        <v>4200.745</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>2866.716202171554</v>
+        <v>4282.481444091797</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="n"/>
       <c r="G41" s="3" t="n"/>
       <c r="H41" s="3" t="n"/>
       <c r="I41" s="3" t="n"/>
@@ -3902,30 +3826,26 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Q2-004</t>
+          <t>Q2-006</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>S013:handover</t>
+          <t>leg1:cruise</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>2866.716202171554</v>
+        <v>4282.481444091797</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>3046.716202171554</v>
+        <v>4572.839269872389</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="n"/>
       <c r="G42" s="3" t="n"/>
       <c r="H42" s="3" t="n"/>
       <c r="I42" s="3" t="n"/>
@@ -3947,19 +3867,19 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Q2-004</t>
+          <t>Q2-006</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>leg2:climb</t>
+          <t>leg1:cruise</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>3046.716202171554</v>
+        <v>4572.839269872389</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>3097.506326683272</v>
+        <v>4821.083651586676</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
@@ -3968,7 +3888,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R03</t>
         </is>
       </c>
       <c r="G43" s="3" t="n"/>
@@ -3992,19 +3912,19 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Q2-004</t>
+          <t>Q2-006</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>leg2:cruise</t>
+          <t>leg1:descent</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>3097.506326683272</v>
+        <v>4821.083651586676</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>3212.395707487873</v>
+        <v>4861.887384496832</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
@@ -4013,7 +3933,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R03</t>
         </is>
       </c>
       <c r="G44" s="3" t="n"/>
@@ -4037,19 +3957,19 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Q2-004</t>
+          <t>Q2-006</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>leg2:descent</t>
+          <t>S008:handover</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>3212.395707487873</v>
+        <v>4861.887384496832</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>3273.383856901935</v>
+        <v>5071.887384496832</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
@@ -4058,7 +3978,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R03</t>
         </is>
       </c>
       <c r="G45" s="3" t="n"/>
@@ -4082,19 +4002,19 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Q2-004</t>
+          <t>Q2-006</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>S010:handover</t>
+          <t>leg2:climb</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>3273.383856901935</v>
+        <v>5071.887384496832</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>3453.383856901935</v>
+        <v>5105.890495255296</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
@@ -4103,7 +4023,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R03</t>
         </is>
       </c>
       <c r="G46" s="3" t="n"/>
@@ -4127,19 +4047,19 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Q2-004</t>
+          <t>Q2-006</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>leg3:climb</t>
+          <t>leg2:cruise</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>3453.383856901935</v>
+        <v>5105.890495255296</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>3481.396035450112</v>
+        <v>5221.483776446192</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
@@ -4148,7 +4068,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R03</t>
         </is>
       </c>
       <c r="G47" s="3" t="n"/>
@@ -4172,19 +4092,19 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Q2-004</t>
+          <t>Q2-006</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>leg3:cruise</t>
+          <t>leg2:cruise</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>3481.396035450112</v>
+        <v>5221.483776446192</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>3551.294905507106</v>
+        <v>5354.134876969582</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
@@ -4193,7 +4113,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R04</t>
         </is>
       </c>
       <c r="G48" s="3" t="n"/>
@@ -4217,19 +4137,19 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Q2-004</t>
+          <t>Q2-006</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>leg3:cruise</t>
+          <t>leg2:cruise</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>3551.294905507106</v>
+        <v>5354.134876969582</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>3880.103939753748</v>
+        <v>5644.492702750174</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
@@ -4258,19 +4178,19 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Q2-004</t>
+          <t>Q2-006</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>leg3:descent</t>
+          <t>leg2:descent</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>3880.103939753748</v>
+        <v>5644.492702750174</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>4003.278554011561</v>
+        <v>5742.57643566033</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
@@ -4299,7 +4219,7 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Q2-005</t>
+          <t>Q2-007</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -4308,10 +4228,10 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>2432.64</v>
+        <v>4360.563</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>2493.058084716797</v>
+        <v>4426.799962890625</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
@@ -4340,7 +4260,7 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Q2-005</t>
+          <t>Q2-007</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -4349,10 +4269,10 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>2493.058084716797</v>
+        <v>4426.799962890625</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>2756.596337115592</v>
+        <v>4756.150707865008</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
@@ -4381,7 +4301,7 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Q2-005</t>
+          <t>Q2-007</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -4390,10 +4310,10 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>2756.596337115592</v>
+        <v>4756.150707865008</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>2987.145448389076</v>
+        <v>4866.850540963379</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
@@ -4402,7 +4322,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R03</t>
         </is>
       </c>
       <c r="G53" s="3" t="n"/>
@@ -4426,7 +4346,7 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Q2-005</t>
+          <t>Q2-007</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
@@ -4435,10 +4355,10 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>2987.145448389076</v>
+        <v>4866.850540963379</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>3022.927150049232</v>
+        <v>4919.414896432129</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
@@ -4447,7 +4367,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R03</t>
         </is>
       </c>
       <c r="G54" s="3" t="n"/>
@@ -4471,19 +4391,19 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Q2-005</t>
+          <t>Q2-007</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>S002:handover</t>
+          <t>S005:handover</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>3022.927150049232</v>
+        <v>4919.414896432129</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>3202.927150049232</v>
+        <v>5099.414896432129</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
@@ -4492,7 +4412,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R03</t>
         </is>
       </c>
       <c r="G55" s="3" t="n"/>
@@ -4516,7 +4436,7 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Q2-005</t>
+          <t>Q2-007</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
@@ -4525,10 +4445,10 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>3202.927150049232</v>
+        <v>5099.414896432129</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>3232.745234766029</v>
+        <v>5167.153344582528</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
@@ -4537,7 +4457,7 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R03</t>
         </is>
       </c>
       <c r="G56" s="3" t="n"/>
@@ -4561,30 +4481,26 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Q2-005</t>
+          <t>Q2-007</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>leg2:cruise</t>
+          <t>leg2:climb</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>3232.745234766029</v>
+        <v>5167.153344582528</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>3463.294346039513</v>
+        <v>5206.797505481609</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="n"/>
       <c r="G57" s="3" t="n"/>
       <c r="H57" s="3" t="n"/>
       <c r="I57" s="3" t="n"/>
@@ -4606,7 +4522,7 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Q2-005</t>
+          <t>Q2-007</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
@@ -4615,10 +4531,10 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>3463.294346039513</v>
+        <v>5206.797505481609</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>3726.832598438308</v>
+        <v>5369.136810753022</v>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
@@ -4647,26 +4563,30 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Q2-005</t>
+          <t>Q2-007</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>leg2:descent</t>
+          <t>leg2:cruise</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>3726.832598438308</v>
+        <v>5369.136810753022</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>3799.334300098464</v>
+        <v>5597.461607312584</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R04</t>
+        </is>
+      </c>
       <c r="G59" s="3" t="n"/>
       <c r="H59" s="3" t="n"/>
       <c r="I59" s="3" t="n"/>
@@ -4688,26 +4608,30 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-007</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>leg1:climb</t>
+          <t>leg2:descent</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>5512.323</v>
+        <v>5597.461607312584</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>5567.499304117839</v>
+        <v>5664.92073817196</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R04</t>
+        </is>
+      </c>
       <c r="G60" s="3" t="n"/>
       <c r="H60" s="3" t="n"/>
       <c r="I60" s="3" t="n"/>
@@ -4729,26 +4653,30 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-007</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>leg1:cruise</t>
+          <t>S007:handover</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>5567.499304117839</v>
+        <v>5664.92073817196</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>5896.949928911088</v>
+        <v>5844.92073817196</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R04</t>
+        </is>
+      </c>
       <c r="G61" s="3" t="n"/>
       <c r="H61" s="3" t="n"/>
       <c r="I61" s="3" t="n"/>
@@ -4770,19 +4698,19 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-007</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>leg1:cruise</t>
+          <t>leg3:climb</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>5896.949928911088</v>
+        <v>5844.92073817196</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>6042.928050974258</v>
+        <v>5899.411796521569</v>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
@@ -4815,19 +4743,19 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-007</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>leg1:descent</t>
+          <t>leg3:cruise</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>6042.928050974258</v>
+        <v>5899.411796521569</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>6068.219615915665</v>
+        <v>5948.988715334517</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
@@ -4860,30 +4788,26 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-007</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>S009:handover</t>
+          <t>leg3:cruise</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>6068.219615915665</v>
+        <v>5948.988715334517</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>6248.219615915665</v>
+        <v>6277.283510422909</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F64" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R04</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="n"/>
       <c r="G64" s="3" t="n"/>
       <c r="H64" s="3" t="n"/>
       <c r="I64" s="3" t="n"/>
@@ -4905,30 +4829,26 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-007</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>leg2:climb</t>
+          <t>leg3:descent</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>6248.219615915665</v>
+        <v>6277.283510422909</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>6280.981833119441</v>
+        <v>6430.992780442441</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R04</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="n"/>
       <c r="G65" s="3" t="n"/>
       <c r="H65" s="3" t="n"/>
       <c r="I65" s="3" t="n"/>
@@ -4950,30 +4870,26 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-008</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>leg2:cruise</t>
+          <t>leg1:climb</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>6280.981833119441</v>
+        <v>4771.262</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>6424.694099441507</v>
+        <v>4944.903655273437</v>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R04</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="n"/>
       <c r="G66" s="3" t="n"/>
       <c r="H66" s="3" t="n"/>
       <c r="I66" s="3" t="n"/>
@@ -4995,30 +4911,26 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-008</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>leg2:descent</t>
+          <t>leg1:cruise</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>6424.694099441507</v>
+        <v>4944.903655273437</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>6468.208760086039</v>
+        <v>5207.195544275051</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R04</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="n"/>
       <c r="G67" s="3" t="n"/>
       <c r="H67" s="3" t="n"/>
       <c r="I67" s="3" t="n"/>
@@ -5040,19 +4952,19 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-008</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>S002:handover</t>
+          <t>leg1:cruise</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>6468.208760086039</v>
+        <v>5207.195544275051</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>6648.208760086039</v>
+        <v>5429.115605710537</v>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
@@ -5085,19 +4997,19 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-008</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>leg3:climb</t>
+          <t>leg1:descent</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>6648.208760086039</v>
+        <v>5429.115605710537</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>6673.027</v>
+        <v>5540.767674802334</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
@@ -5130,19 +5042,19 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-008</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>leg3:climb</t>
+          <t>S003:handover</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>6673.027</v>
+        <v>5540.767674802334</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>6678.026844802836</v>
+        <v>5936.767674802334</v>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
@@ -5151,7 +5063,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>Q3-R05</t>
+          <t>Q3-R04</t>
         </is>
       </c>
       <c r="G70" s="3" t="n"/>
@@ -5175,19 +5087,19 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-008</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>leg3:cruise</t>
+          <t>leg2:climb</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>6678.026844802836</v>
+        <v>5936.767674802334</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>6966.211147875548</v>
+        <v>6026.089330075772</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
@@ -5196,7 +5108,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>Q3-R05</t>
+          <t>Q3-R04</t>
         </is>
       </c>
       <c r="G71" s="3" t="n"/>
@@ -5220,26 +5132,30 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-008</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>leg3:cruise</t>
+          <t>leg2:cruise</t>
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>6966.211147875548</v>
+        <v>6026.089330075772</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>7295.636049393184</v>
+        <v>6248.009391511257</v>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F72" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R04</t>
+        </is>
+      </c>
       <c r="G72" s="3" t="n"/>
       <c r="H72" s="3" t="n"/>
       <c r="I72" s="3" t="n"/>
@@ -5261,19 +5177,19 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-008</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>leg3:descent</t>
+          <t>leg2:cruise</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>7295.636049393184</v>
+        <v>6248.009391511257</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>7368.13775105334</v>
+        <v>6510.301280512872</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
@@ -5302,19 +5218,19 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>Q2-007</t>
+          <t>Q2-008</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>leg1:climb</t>
+          <t>leg2:descent</t>
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>425.366</v>
+        <v>6510.301280512872</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>553.4570583496094</v>
+        <v>6727.353349604668</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
@@ -5343,19 +5259,19 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Q2-007</t>
+          <t>Q2-009</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>leg1:cruise</t>
+          <t>leg1:climb</t>
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>553.4570583496094</v>
+        <v>360</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>816.0935140446727</v>
+        <v>514.7491292317709</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
@@ -5384,7 +5300,7 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Q2-007</t>
+          <t>Q2-009</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
@@ -5393,21 +5309,17 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>816.0935140446727</v>
+        <v>514.7491292317709</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>855.754429470681</v>
+        <v>842.3521146428054</v>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F76" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="n"/>
       <c r="G76" s="3" t="n"/>
       <c r="H76" s="3" t="n"/>
       <c r="I76" s="3" t="n"/>
@@ -5429,19 +5341,19 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Q2-007</t>
+          <t>Q2-009</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>leg1:descent</t>
+          <t>leg1:cruise</t>
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>855.754429470681</v>
+        <v>842.3521146428054</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>921.1436994902123</v>
+        <v>966.3826174161993</v>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
@@ -5450,7 +5362,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>Q3-R01</t>
+          <t>Q3-R02</t>
         </is>
       </c>
       <c r="G77" s="3" t="n"/>
@@ -5474,19 +5386,19 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>Q2-007</t>
+          <t>Q2-009</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>S007:handover</t>
+          <t>leg1:descent</t>
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>921.1436994902123</v>
+        <v>966.3826174161993</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>1131.143699490212</v>
+        <v>1062.761572494324</v>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
@@ -5495,7 +5407,7 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>Q3-R01</t>
+          <t>Q3-R02</t>
         </is>
       </c>
       <c r="G78" s="3" t="n"/>
@@ -5519,19 +5431,19 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>Q2-007</t>
+          <t>Q2-009</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>leg2:climb</t>
+          <t>S014:handover</t>
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>1131.143699490212</v>
+        <v>1062.761572494324</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>1185.634757839822</v>
+        <v>1272.761572494324</v>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
@@ -5540,7 +5452,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>Q3-R01</t>
+          <t>Q3-R02</t>
         </is>
       </c>
       <c r="G79" s="3" t="n"/>
@@ -5564,19 +5476,19 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>Q2-007</t>
+          <t>Q2-009</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>leg2:cruise</t>
+          <t>leg2:climb</t>
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>1185.634757839822</v>
+        <v>1272.761572494324</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>1225.29567326583</v>
+        <v>1353.077368392762</v>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
@@ -5585,14 +5497,14 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>Q3-R01</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Q2-007</t>
+          <t>Q2-009</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -5601,34 +5513,38 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>1225.29567326583</v>
+        <v>1353.077368392762</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>1487.932128960893</v>
+        <v>1477.107871166156</v>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F81" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>Q2-007</t>
+          <t>Q2-009</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>leg2:descent</t>
+          <t>leg2:cruise</t>
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>1487.932128960893</v>
+        <v>1477.107871166156</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>1641.641398980425</v>
+        <v>1804.71085657719</v>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
@@ -5640,19 +5556,19 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>Q2-008</t>
+          <t>Q2-009</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>leg1:climb</t>
+          <t>leg2:descent</t>
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>360</v>
+        <v>1804.71085657719</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>439.4659464518229</v>
+        <v>1990.409811655315</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
@@ -5664,19 +5580,19 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>Q2-008</t>
+          <t>Q2-010</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>leg1:cruise</t>
+          <t>leg1:climb</t>
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>439.4659464518229</v>
+        <v>4734.632</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>704.9832946529609</v>
+        <v>4879.333379394531</v>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
@@ -5688,19 +5604,19 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>Q2-008</t>
+          <t>Q2-010</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>leg1:descent</t>
+          <t>leg1:cruise</t>
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>704.9832946529609</v>
+        <v>4879.333379394531</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>725.5024303951484</v>
+        <v>5207.206046081916</v>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
@@ -5712,163 +5628,187 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>Q2-008</t>
+          <t>Q2-010</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>S006:handover</t>
+          <t>leg1:cruise</t>
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>725.5024303951484</v>
+        <v>5207.206046081916</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>935.5024303951484</v>
+        <v>5484.598317440907</v>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F86" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R04</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>Q2-008</t>
+          <t>Q2-010</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>leg2:climb</t>
+          <t>leg1:descent</t>
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>935.5024303951484</v>
+        <v>5484.598317440907</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>952.6017101803046</v>
+        <v>5573.919972714344</v>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F87" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R04</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>Q2-008</t>
+          <t>Q2-010</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>leg2:cruise</t>
+          <t>S003:handover</t>
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>952.6017101803046</v>
+        <v>5573.919972714344</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>1218.119058381443</v>
+        <v>5753.919972714344</v>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F88" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R04</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>Q2-008</t>
+          <t>Q2-010</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>leg2:descent</t>
+          <t>leg2:climb</t>
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>1218.119058381443</v>
+        <v>5753.919972714344</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>1313.47819412363</v>
+        <v>5803.719594296375</v>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F89" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R04</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-010</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>leg1:climb</t>
+          <t>leg2:cruise</t>
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>426.247</v>
+        <v>5803.719594296375</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>516.7409412434896</v>
+        <v>6021.750169370585</v>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F90" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R04</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-010</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>leg1:cruise</t>
+          <t>leg2:descent</t>
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>516.7409412434896</v>
+        <v>6021.750169370585</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>845.7466921002185</v>
+        <v>6027.109715269023</v>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F91" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R04</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-010</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>leg1:cruise</t>
+          <t>S015:handover</t>
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>845.7466921002185</v>
+        <v>6027.109715269023</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>920.8444726793655</v>
+        <v>6237.109715269023</v>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
@@ -5877,26 +5817,26 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R04</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-010</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>leg1:descent</t>
+          <t>leg3:climb</t>
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>920.8444726793655</v>
+        <v>6237.109715269023</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>939.837202171553</v>
+        <v>6269.542800392721</v>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
@@ -5905,26 +5845,26 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R04</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-010</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>S013:handover</t>
+          <t>leg3:cruise</t>
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>939.837202171553</v>
+        <v>6269.542800392721</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>1119.837202171553</v>
+        <v>6442.529966148881</v>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
@@ -5933,138 +5873,122 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R04</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-010</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>leg2:climb</t>
+          <t>leg3:cruise</t>
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>1119.837202171553</v>
+        <v>6442.529966148881</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>1170.627326683272</v>
+        <v>6770.324714694411</v>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F95" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-010</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>leg2:cruise</t>
+          <t>leg3:descent</t>
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>1170.627326683272</v>
+        <v>6770.324714694411</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>1285.516707487873</v>
+        <v>6947.964416842849</v>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F96" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-011</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>leg2:descent</t>
+          <t>leg1:climb</t>
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>1285.516707487873</v>
+        <v>3337.509</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>1346.504856901935</v>
+        <v>3427.688722086589</v>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F97" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-011</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>S010:handover</t>
+          <t>leg1:cruise</t>
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>1346.504856901935</v>
+        <v>3427.688722086589</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>1556.504856901935</v>
+        <v>3800.0534033041</v>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F98" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-011</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>leg3:climb</t>
+          <t>leg1:cruise</t>
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>1556.504856901935</v>
+        <v>3800.0534033041</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>1584.517035450112</v>
+        <v>3942.0018186944</v>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
@@ -6073,26 +5997,26 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R03</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-011</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>leg3:cruise</t>
+          <t>leg1:descent</t>
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>1584.517035450112</v>
+        <v>3942.0018186944</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>1654.415905507106</v>
+        <v>4009.977485198306</v>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
@@ -6101,98 +6025,110 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R03</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-011</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>leg3:cruise</t>
+          <t>S004:handover</t>
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>1654.415905507106</v>
+        <v>4009.977485198306</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>1983.224939753748</v>
+        <v>4189.977485198306</v>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F101" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R03</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-011</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>leg3:descent</t>
+          <t>leg2:climb</t>
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>1983.224939753748</v>
+        <v>4189.977485198306</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>2106.399554011561</v>
+        <v>4246.623873951561</v>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F102" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R03</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>Q2-010</t>
+          <t>Q2-011</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>leg1:climb</t>
+          <t>leg2:cruise</t>
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>4788.57</v>
+        <v>4246.623873951561</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>4843.746304117838</v>
+        <v>4388.572289341861</v>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F103" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R03</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>Q2-010</t>
+          <t>Q2-011</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>leg1:cruise</t>
+          <t>leg2:cruise</t>
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>4843.746304117838</v>
+        <v>4388.572289341861</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>5173.196928911088</v>
+        <v>4760.936970559373</v>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
@@ -6204,103 +6140,91 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>Q2-010</t>
+          <t>Q2-011</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>leg1:cruise</t>
+          <t>leg2:descent</t>
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>5173.196928911088</v>
+        <v>4760.936970559373</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>5178.351</v>
+        <v>4869.152637063279</v>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F105" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R03</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>Q2-010</t>
+          <t>Q2-012</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>leg1:cruise</t>
+          <t>leg1:climb</t>
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>5178.351</v>
+        <v>2444.05</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>5319.175050974258</v>
+        <v>2504.468084716797</v>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F106" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R04</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>Q2-010</t>
+          <t>Q2-012</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>leg1:descent</t>
+          <t>leg1:cruise</t>
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>5319.175050974258</v>
+        <v>2504.468084716797</v>
       </c>
       <c r="D107" s="4" t="n">
-        <v>5344.466615915664</v>
+        <v>2768.006337115592</v>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F107" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R04</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>Q2-010</t>
+          <t>Q2-012</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>S009:handover</t>
+          <t>leg1:cruise</t>
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>5344.466615915664</v>
+        <v>2768.006337115592</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>5524.466615915664</v>
+        <v>2998.555448389076</v>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
@@ -6309,26 +6233,26 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>Q3-R04</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>Q2-010</t>
+          <t>Q2-012</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>leg2:climb</t>
+          <t>leg1:descent</t>
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>5524.466615915664</v>
+        <v>2998.555448389076</v>
       </c>
       <c r="D109" s="4" t="n">
-        <v>5568.987683217097</v>
+        <v>3034.337150049232</v>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
@@ -6337,26 +6261,26 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>Q3-R04</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>Q2-010</t>
+          <t>Q2-012</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>leg2:cruise</t>
+          <t>S002:handover</t>
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>5568.987683217097</v>
+        <v>3034.337150049232</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>5789.814561283163</v>
+        <v>3244.337150049232</v>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
@@ -6365,26 +6289,26 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>Q3-R04</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>Q2-010</t>
+          <t>Q2-012</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>leg2:descent</t>
+          <t>leg2:climb</t>
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>5789.814561283163</v>
+        <v>3244.337150049232</v>
       </c>
       <c r="D111" s="4" t="n">
-        <v>5857.239842044882</v>
+        <v>3274.155234766029</v>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
@@ -6393,26 +6317,26 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>Q3-R04</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>Q2-010</t>
+          <t>Q2-012</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>S005:handover</t>
+          <t>leg2:cruise</t>
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>5857.239842044882</v>
+        <v>3274.155234766029</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>6067.239842044882</v>
+        <v>3504.704346039513</v>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
@@ -6421,82 +6345,74 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>Q3-R04</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>Q2-010</t>
+          <t>Q2-012</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>leg3:climb</t>
+          <t>leg2:cruise</t>
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>6067.239842044882</v>
+        <v>3504.704346039513</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>6111.043471602174</v>
+        <v>3768.242598438308</v>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F113" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R04</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>Q2-010</t>
+          <t>Q2-012</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>leg3:cruise</t>
+          <t>leg2:descent</t>
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>6111.043471602174</v>
+        <v>3768.242598438308</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>6221.743304700543</v>
+        <v>3840.744300098464</v>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F114" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R04</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>Q2-010</t>
+          <t>Q2-013</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>leg3:cruise</t>
+          <t>leg1:climb</t>
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>6221.743304700543</v>
+        <v>5887.208</v>
       </c>
       <c r="D115" s="4" t="n">
-        <v>6551.094049674927</v>
+        <v>5943.095251790364</v>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
@@ -6508,19 +6424,19 @@
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>Q2-010</t>
+          <t>Q2-013</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>leg3:descent</t>
+          <t>leg1:cruise</t>
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>6551.094049674927</v>
+        <v>5943.095251790364</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>6630.578405143678</v>
+        <v>6177.101437847168</v>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
@@ -6532,19 +6448,19 @@
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>Q2-011</t>
+          <t>Q2-013</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>leg1:climb</t>
+          <t>leg1:descent</t>
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>4701.047</v>
+        <v>6177.101437847168</v>
       </c>
       <c r="D117" s="4" t="n">
-        <v>4845.748379394531</v>
+        <v>6210.406139995605</v>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
@@ -6556,19 +6472,19 @@
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>Q2-011</t>
+          <t>Q2-013</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>leg1:cruise</t>
+          <t>S011:handover</t>
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>4845.748379394531</v>
+        <v>6210.406139995605</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>5173.621046081916</v>
+        <v>6390.406139995605</v>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
@@ -6580,159 +6496,139 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>Q2-011</t>
+          <t>Q2-013</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>leg1:cruise</t>
+          <t>leg2:climb</t>
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>5173.621046081916</v>
+        <v>6390.406139995605</v>
       </c>
       <c r="D119" s="4" t="n">
-        <v>5451.013317440907</v>
+        <v>6418.160058452637</v>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F119" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R04</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>Q2-011</t>
+          <t>Q2-013</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>leg1:descent</t>
+          <t>leg2:cruise</t>
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>5451.013317440907</v>
+        <v>6418.160058452637</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>5540.334972714344</v>
+        <v>6652.166244509441</v>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F120" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R04</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>Q2-011</t>
+          <t>Q2-013</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>S003:handover</t>
+          <t>leg2:descent</t>
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>5540.334972714344</v>
+        <v>6652.166244509441</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>5720.334972714344</v>
+        <v>6719.230946657878</v>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F121" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R04</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>Q2-011</t>
+          <t>Q2-014</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>leg2:climb</t>
+          <t>leg1:climb</t>
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>5720.334972714344</v>
+        <v>360</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>5770.134594296375</v>
+        <v>488.0910583496094</v>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F122" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R04</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>Q2-011</t>
+          <t>Q2-014</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>leg2:cruise</t>
+          <t>leg1:cruise</t>
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>5770.134594296375</v>
+        <v>488.0910583496094</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>5988.165169370585</v>
+        <v>816.3858534380004</v>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F123" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R04</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>Q2-011</t>
+          <t>Q2-014</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>leg2:descent</t>
+          <t>leg1:cruise</t>
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>5988.165169370585</v>
+        <v>816.3858534380004</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>5993.524715269023</v>
+        <v>865.9627722509489</v>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
@@ -6741,26 +6637,26 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>Q3-R04</t>
+          <t>Q3-R01</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>Q2-011</t>
+          <t>Q2-014</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>S015:handover</t>
+          <t>leg1:descent</t>
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>5993.524715269023</v>
+        <v>865.9627722509489</v>
       </c>
       <c r="D125" s="4" t="n">
-        <v>6203.524715269023</v>
+        <v>931.3520422704802</v>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
@@ -6769,26 +6665,26 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>Q3-R04</t>
+          <t>Q3-R01</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>Q2-011</t>
+          <t>Q2-014</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>leg3:climb</t>
+          <t>S007:handover</t>
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>6203.524715269023</v>
+        <v>931.3520422704802</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>6235.957800392721</v>
+        <v>1111.35204227048</v>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
@@ -6797,26 +6693,26 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>Q3-R04</t>
+          <t>Q3-R01</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>Q2-011</t>
+          <t>Q2-014</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>leg3:cruise</t>
+          <t>leg2:climb</t>
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>6235.957800392721</v>
+        <v>1111.35204227048</v>
       </c>
       <c r="D127" s="4" t="n">
-        <v>6408.944966148881</v>
+        <v>1132.085155877251</v>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
@@ -6825,146 +6721,166 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>Q3-R04</t>
+          <t>Q3-R01</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>Q2-011</t>
+          <t>Q2-014</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>leg3:cruise</t>
+          <t>leg2:cruise</t>
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>6408.944966148881</v>
+        <v>1132.085155877251</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>6736.739714694411</v>
+        <v>1359.940291110606</v>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F128" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>Q2-011</t>
+          <t>Q2-014</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>leg3:descent</t>
+          <t>leg2:descent</t>
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>6736.739714694411</v>
+        <v>1359.940291110606</v>
       </c>
       <c r="D129" s="4" t="n">
-        <v>6914.379416842849</v>
+        <v>1388.820027438731</v>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F129" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>Q2-012</t>
+          <t>Q2-014</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>leg1:climb</t>
+          <t>S003:handover</t>
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>2582.308</v>
+        <v>1388.820027438731</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>2640.450644042969</v>
+        <v>1568.820027438731</v>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F130" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>Q2-012</t>
+          <t>Q2-014</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>leg1:cruise</t>
+          <t>leg3:climb</t>
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>2640.450644042969</v>
+        <v>1568.820027438731</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>2844.049233610869</v>
+        <v>1643.254740166595</v>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F131" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>Q2-012</t>
+          <t>Q2-014</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>leg1:descent</t>
+          <t>leg3:cruise</t>
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>2844.049233610869</v>
+        <v>1643.254740166595</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>2888.57753866458</v>
+        <v>1920.647011525587</v>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F132" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>Q2-012</t>
+          <t>Q2-014</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>S001:handover</t>
+          <t>leg3:cruise</t>
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>2888.57753866458</v>
+        <v>1920.647011525587</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>3320.57753866458</v>
+        <v>2248.519678212971</v>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
@@ -6976,19 +6892,19 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>Q2-012</t>
+          <t>Q2-014</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>leg2:climb</t>
+          <t>leg3:descent</t>
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>3320.57753866458</v>
+        <v>2248.519678212971</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>3356.200182707548</v>
+        <v>2422.161333486408</v>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
@@ -7000,19 +6916,19 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>Q2-012</t>
+          <t>Q2-015</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>leg2:cruise</t>
+          <t>leg1:climb</t>
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>3356.200182707548</v>
+        <v>2619.758</v>
       </c>
       <c r="D135" s="4" t="n">
-        <v>3559.798772275448</v>
+        <v>2680.176084716797</v>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
@@ -7024,19 +6940,19 @@
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>Q2-012</t>
+          <t>Q2-015</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>leg2:descent</t>
+          <t>leg1:cruise</t>
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>3559.798772275448</v>
+        <v>2680.176084716797</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>3632.477077329159</v>
+        <v>3009.600986234433</v>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
@@ -7048,67 +6964,75 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>Q2-013</t>
+          <t>Q2-015</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>leg1:climb</t>
+          <t>leg1:cruise</t>
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>425.366</v>
+        <v>3009.600986234433</v>
       </c>
       <c r="D137" s="4" t="n">
-        <v>553.4570583496094</v>
+        <v>3297.785289307145</v>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F137" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>Q2-013</t>
+          <t>Q2-015</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>leg1:cruise</t>
+          <t>leg1:descent</t>
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>553.4570583496094</v>
+        <v>3297.785289307145</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>816.0935140446727</v>
+        <v>3333.566990967301</v>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F138" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>Q2-013</t>
+          <t>Q2-015</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>leg1:cruise</t>
+          <t>S002:handover</t>
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>816.0935140446727</v>
+        <v>3333.566990967301</v>
       </c>
       <c r="D139" s="4" t="n">
-        <v>855.754429470681</v>
+        <v>3513.566990967301</v>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
@@ -7117,26 +7041,26 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>Q3-R01</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>Q2-013</t>
+          <t>Q2-015</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>leg1:descent</t>
+          <t>leg2:climb</t>
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>855.754429470681</v>
+        <v>3513.566990967301</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>921.1436994902123</v>
+        <v>3546.62</v>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
@@ -7145,26 +7069,26 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>Q3-R01</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>Q2-013</t>
+          <t>Q2-015</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>S007:handover</t>
+          <t>leg2:climb</t>
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>921.1436994902123</v>
+        <v>3546.62</v>
       </c>
       <c r="D141" s="4" t="n">
-        <v>1101.143699490212</v>
+        <v>3551.619725342301</v>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
@@ -7173,26 +7097,26 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>Q3-R01</t>
+          <t>Q3-R03</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>Q2-013</t>
+          <t>Q2-015</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>leg2:climb</t>
+          <t>leg2:cruise</t>
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>1101.143699490212</v>
+        <v>3551.619725342301</v>
       </c>
       <c r="D142" s="4" t="n">
-        <v>1152.616437120421</v>
+        <v>3738.954533524521</v>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
@@ -7201,26 +7125,26 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>Q3-R01</t>
+          <t>Q3-R03</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>Q2-013</t>
+          <t>Q2-015</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>leg2:cruise</t>
+          <t>leg2:descent</t>
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>1152.616437120421</v>
+        <v>3738.954533524521</v>
       </c>
       <c r="D143" s="4" t="n">
-        <v>1300.573732581262</v>
+        <v>3781.097814774521</v>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
@@ -7229,26 +7153,26 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>Q3-R01</t>
+          <t>Q3-R03</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>Q2-013</t>
+          <t>Q2-015</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>leg2:descent</t>
+          <t>S004:handover</t>
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>1300.573732581262</v>
+        <v>3781.097814774521</v>
       </c>
       <c r="D144" s="4" t="n">
-        <v>1311.941017737513</v>
+        <v>3991.097814774521</v>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
@@ -7257,26 +7181,26 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>Q3-R01</t>
+          <t>Q3-R03</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>Q2-013</t>
+          <t>Q2-015</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>S015:handover</t>
+          <t>leg3:climb</t>
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>1311.941017737513</v>
+        <v>3991.097814774521</v>
       </c>
       <c r="D145" s="4" t="n">
-        <v>1491.941017737513</v>
+        <v>4047.744203527776</v>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
@@ -7285,26 +7209,26 @@
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>Q3-R01</t>
+          <t>Q3-R03</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>Q2-013</t>
+          <t>Q2-015</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>leg3:climb</t>
+          <t>leg3:cruise</t>
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>1491.941017737513</v>
+        <v>4047.744203527776</v>
       </c>
       <c r="D146" s="4" t="n">
-        <v>1524.374102861211</v>
+        <v>4225.151727010179</v>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
@@ -7313,14 +7237,14 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>Q3-R01</t>
+          <t>Q3-R03</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>Q2-013</t>
+          <t>Q2-015</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
@@ -7329,38 +7253,34 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>1524.374102861211</v>
+        <v>4225.151727010179</v>
       </c>
       <c r="D147" s="4" t="n">
-        <v>1662.768605690686</v>
+        <v>4690.63557428754</v>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F147" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F147" s="3" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>Q2-013</t>
+          <t>Q2-015</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>leg3:cruise</t>
+          <t>leg3:descent</t>
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>1662.768605690686</v>
+        <v>4690.63557428754</v>
       </c>
       <c r="D148" s="4" t="n">
-        <v>1924.999634302563</v>
+        <v>4798.851240791447</v>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
@@ -7372,19 +7292,19 @@
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>Q2-013</t>
+          <t>Q2-016</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>leg3:descent</t>
+          <t>leg1:climb</t>
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>1924.999634302563</v>
+        <v>2350.41</v>
       </c>
       <c r="D149" s="4" t="n">
-        <v>2102.639336451001</v>
+        <v>2440.903941243489</v>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
@@ -7396,19 +7316,19 @@
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>Q2-014</t>
+          <t>Q2-016</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>leg1:climb</t>
+          <t>leg1:cruise</t>
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>5750.738</v>
+        <v>2440.903941243489</v>
       </c>
       <c r="D150" s="4" t="n">
-        <v>5806.625251790365</v>
+        <v>2769.909692100218</v>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
@@ -7420,7 +7340,7 @@
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>Q2-014</t>
+          <t>Q2-016</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
@@ -7429,22 +7349,26 @@
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>5806.625251790365</v>
+        <v>2769.909692100218</v>
       </c>
       <c r="D151" s="4" t="n">
-        <v>6040.631437847169</v>
+        <v>2845.007472679365</v>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F151" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>Q2-014</t>
+          <t>Q2-016</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
@@ -7453,46 +7377,54 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>6040.631437847169</v>
+        <v>2845.007472679365</v>
       </c>
       <c r="D152" s="4" t="n">
-        <v>6073.936139995606</v>
+        <v>2864.000202171553</v>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F152" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>Q2-014</t>
+          <t>Q2-016</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>S011:handover</t>
+          <t>S013:handover</t>
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>6073.936139995606</v>
+        <v>2864.000202171553</v>
       </c>
       <c r="D153" s="4" t="n">
-        <v>6253.936139995606</v>
+        <v>3044.000202171553</v>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F153" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>Q2-014</t>
+          <t>Q2-016</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
@@ -7501,22 +7433,26 @@
         </is>
       </c>
       <c r="C154" s="4" t="n">
-        <v>6253.936139995606</v>
+        <v>3044.000202171553</v>
       </c>
       <c r="D154" s="4" t="n">
-        <v>6329.627924663575</v>
+        <v>3094.790326683272</v>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F154" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>Q2-014</t>
+          <t>Q2-016</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
@@ -7525,34 +7461,38 @@
         </is>
       </c>
       <c r="C155" s="4" t="n">
-        <v>6329.627924663575</v>
+        <v>3094.790326683272</v>
       </c>
       <c r="D155" s="4" t="n">
-        <v>6502.193767966894</v>
+        <v>3209.679707487873</v>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F155" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>Q2-014</t>
+          <t>Q2-016</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>leg2:cruise</t>
+          <t>leg2:descent</t>
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>6502.193767966894</v>
+        <v>3209.679707487873</v>
       </c>
       <c r="D156" s="4" t="n">
-        <v>6565.796964376301</v>
+        <v>3270.667856901935</v>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
@@ -7561,26 +7501,26 @@
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>Q3-R04</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>Q2-014</t>
+          <t>Q2-016</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>leg2:descent</t>
+          <t>S010:handover</t>
         </is>
       </c>
       <c r="C157" s="4" t="n">
-        <v>6565.796964376301</v>
+        <v>3270.667856901935</v>
       </c>
       <c r="D157" s="4" t="n">
-        <v>6602.067105977863</v>
+        <v>3450.667856901935</v>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
@@ -7589,26 +7529,26 @@
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>Q3-R04</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>Q2-014</t>
+          <t>Q2-016</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>S007:handover</t>
+          <t>leg3:climb</t>
         </is>
       </c>
       <c r="C158" s="4" t="n">
-        <v>6602.067105977863</v>
+        <v>3450.667856901935</v>
       </c>
       <c r="D158" s="4" t="n">
-        <v>6782.067105977863</v>
+        <v>3478.680035450112</v>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
@@ -7617,26 +7557,26 @@
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>Q3-R04</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>Q2-014</t>
+          <t>Q2-016</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>leg3:climb</t>
+          <t>leg3:cruise</t>
         </is>
       </c>
       <c r="C159" s="4" t="n">
-        <v>6782.067105977863</v>
+        <v>3478.680035450112</v>
       </c>
       <c r="D159" s="4" t="n">
-        <v>6787.068</v>
+        <v>3548.578905507105</v>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
@@ -7645,82 +7585,74 @@
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>Q3-R04</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>Q2-014</t>
+          <t>Q2-016</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>leg3:climb</t>
+          <t>leg3:cruise</t>
         </is>
       </c>
       <c r="C160" s="4" t="n">
-        <v>6787.068</v>
+        <v>3548.578905507105</v>
       </c>
       <c r="D160" s="4" t="n">
-        <v>6836.558164327473</v>
+        <v>3877.387939753748</v>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F160" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R05</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F160" s="3" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>Q2-014</t>
+          <t>Q2-016</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>leg3:cruise</t>
+          <t>leg3:descent</t>
         </is>
       </c>
       <c r="C161" s="4" t="n">
-        <v>6836.558164327473</v>
+        <v>3877.387939753748</v>
       </c>
       <c r="D161" s="4" t="n">
-        <v>6886.135083140422</v>
+        <v>4000.56255401156</v>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F161" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R05</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F161" s="3" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>Q2-014</t>
+          <t>Q2-017</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>leg3:cruise</t>
+          <t>leg1:climb</t>
         </is>
       </c>
       <c r="C162" s="4" t="n">
-        <v>6886.135083140422</v>
+        <v>6102.577</v>
       </c>
       <c r="D162" s="4" t="n">
-        <v>7214.429878228812</v>
+        <v>6182.042946451823</v>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
@@ -7732,19 +7664,19 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>Q2-014</t>
+          <t>Q2-017</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>leg3:descent</t>
+          <t>leg1:cruise</t>
         </is>
       </c>
       <c r="C163" s="4" t="n">
-        <v>7214.429878228812</v>
+        <v>6182.042946451823</v>
       </c>
       <c r="D163" s="4" t="n">
-        <v>7368.139148248344</v>
+        <v>6394.456825012733</v>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
@@ -7756,19 +7688,19 @@
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>Q2-015</t>
+          <t>Q2-017</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>leg1:climb</t>
+          <t>leg1:descent</t>
         </is>
       </c>
       <c r="C164" s="4" t="n">
-        <v>5742.881</v>
+        <v>6394.456825012733</v>
       </c>
       <c r="D164" s="4" t="n">
-        <v>5824.617444091798</v>
+        <v>6414.97596075492</v>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
@@ -7780,19 +7712,19 @@
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>Q2-015</t>
+          <t>Q2-017</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>leg1:cruise</t>
+          <t>S006:handover</t>
         </is>
       </c>
       <c r="C165" s="4" t="n">
-        <v>5824.617444091798</v>
+        <v>6414.97596075492</v>
       </c>
       <c r="D165" s="4" t="n">
-        <v>6114.97526987239</v>
+        <v>6624.97596075492</v>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
@@ -7804,159 +7736,139 @@
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>Q2-015</t>
+          <t>Q2-017</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>leg1:cruise</t>
+          <t>leg2:climb</t>
         </is>
       </c>
       <c r="C166" s="4" t="n">
-        <v>6114.97526987239</v>
+        <v>6624.97596075492</v>
       </c>
       <c r="D166" s="4" t="n">
-        <v>6363.219651586676</v>
+        <v>6642.075240540076</v>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F166" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R04</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F166" s="3" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>Q2-015</t>
+          <t>Q2-017</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>leg1:descent</t>
+          <t>leg2:cruise</t>
         </is>
       </c>
       <c r="C167" s="4" t="n">
-        <v>6363.219651586676</v>
+        <v>6642.075240540076</v>
       </c>
       <c r="D167" s="4" t="n">
-        <v>6404.023384496832</v>
+        <v>6854.489119100986</v>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F167" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R04</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F167" s="3" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>Q2-015</t>
+          <t>Q2-017</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>S008:handover</t>
+          <t>leg2:descent</t>
         </is>
       </c>
       <c r="C168" s="4" t="n">
-        <v>6404.023384496832</v>
+        <v>6854.489119100986</v>
       </c>
       <c r="D168" s="4" t="n">
-        <v>6644.023384496832</v>
+        <v>6949.848254843174</v>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F168" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R04</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F168" s="3" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>Q2-015</t>
+          <t>Q2-018</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>leg2:climb</t>
+          <t>leg1:climb</t>
         </is>
       </c>
       <c r="C169" s="4" t="n">
-        <v>6644.023384496832</v>
+        <v>4081.983</v>
       </c>
       <c r="D169" s="4" t="n">
-        <v>6678.026495255296</v>
+        <v>4161.467355468751</v>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F169" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R04</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F169" s="3" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>Q2-015</t>
+          <t>Q2-018</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>leg2:cruise</t>
+          <t>leg1:cruise</t>
         </is>
       </c>
       <c r="C170" s="4" t="n">
-        <v>6678.026495255296</v>
+        <v>4161.467355468751</v>
       </c>
       <c r="D170" s="4" t="n">
-        <v>6787.068</v>
+        <v>4424.966768328923</v>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F170" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R04</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F170" s="3" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>Q2-015</t>
+          <t>Q2-018</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>leg2:cruise</t>
+          <t>leg1:cruise</t>
         </is>
       </c>
       <c r="C171" s="4" t="n">
-        <v>6787.068</v>
+        <v>4424.966768328923</v>
       </c>
       <c r="D171" s="4" t="n">
-        <v>6926.270876969583</v>
+        <v>4513.507817926954</v>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
@@ -7965,122 +7877,138 @@
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>Q3-R05</t>
+          <t>Q3-R03</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>Q2-015</t>
+          <t>Q2-018</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>leg2:cruise</t>
+          <t>leg1:descent</t>
         </is>
       </c>
       <c r="C172" s="4" t="n">
-        <v>6926.270876969583</v>
+        <v>4513.507817926954</v>
       </c>
       <c r="D172" s="4" t="n">
-        <v>7216.628702750175</v>
+        <v>4579.213262262891</v>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F172" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F172" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R03</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>Q2-015</t>
+          <t>Q2-018</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>leg2:descent</t>
+          <t>S005:handover</t>
         </is>
       </c>
       <c r="C173" s="4" t="n">
-        <v>7216.628702750175</v>
+        <v>4579.213262262891</v>
       </c>
       <c r="D173" s="4" t="n">
-        <v>7314.712435660331</v>
+        <v>4867.213262262891</v>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F173" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F173" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R03</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>Q2-016</t>
+          <t>Q2-018</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>leg1:climb</t>
+          <t>leg2:climb</t>
         </is>
       </c>
       <c r="C174" s="4" t="n">
-        <v>360</v>
+        <v>4867.213262262891</v>
       </c>
       <c r="D174" s="4" t="n">
-        <v>488.0910583496094</v>
+        <v>4935.535894098829</v>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F174" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F174" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R03</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>Q2-016</t>
+          <t>Q2-018</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>leg1:cruise</t>
+          <t>leg2:cruise</t>
         </is>
       </c>
       <c r="C175" s="4" t="n">
-        <v>488.0910583496094</v>
+        <v>4935.535894098829</v>
       </c>
       <c r="D175" s="4" t="n">
-        <v>816.3858534380004</v>
+        <v>5109.411997663108</v>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F175" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F175" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R03</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>Q2-016</t>
+          <t>Q2-018</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>leg1:cruise</t>
+          <t>leg2:descent</t>
         </is>
       </c>
       <c r="C176" s="4" t="n">
-        <v>816.3858534380004</v>
+        <v>5109.411997663108</v>
       </c>
       <c r="D176" s="4" t="n">
-        <v>865.9627722509489</v>
+        <v>5178.16528745803</v>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
@@ -8089,26 +8017,26 @@
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>Q3-R01</t>
+          <t>Q3-R03</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>Q2-016</t>
+          <t>Q2-018</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>leg1:descent</t>
+          <t>S004:handover</t>
         </is>
       </c>
       <c r="C177" s="4" t="n">
-        <v>865.9627722509489</v>
+        <v>5178.16528745803</v>
       </c>
       <c r="D177" s="4" t="n">
-        <v>931.3520422704802</v>
+        <v>5466.16528745803</v>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
@@ -8117,26 +8045,26 @@
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>Q3-R01</t>
+          <t>Q3-R03</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>Q2-016</t>
+          <t>Q2-018</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>S007:handover</t>
+          <t>leg3:climb</t>
         </is>
       </c>
       <c r="C178" s="4" t="n">
-        <v>931.3520422704802</v>
+        <v>5466.16528745803</v>
       </c>
       <c r="D178" s="4" t="n">
-        <v>1111.35204227048</v>
+        <v>5534.140953961936</v>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
@@ -8145,26 +8073,26 @@
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>Q3-R01</t>
+          <t>Q3-R03</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>Q2-016</t>
+          <t>Q2-018</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>leg2:climb</t>
+          <t>leg3:cruise</t>
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>1111.35204227048</v>
+        <v>5534.140953961936</v>
       </c>
       <c r="D179" s="4" t="n">
-        <v>1132.085155877251</v>
+        <v>5539.141</v>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
@@ -8173,26 +8101,26 @@
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>Q3-R01</t>
+          <t>Q3-R03</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>Q2-016</t>
+          <t>Q2-018</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>leg2:cruise</t>
+          <t>leg3:cruise</t>
         </is>
       </c>
       <c r="C180" s="4" t="n">
-        <v>1132.085155877251</v>
+        <v>5539.141</v>
       </c>
       <c r="D180" s="4" t="n">
-        <v>1359.940291110606</v>
+        <v>5676.089369352236</v>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
@@ -8201,234 +8129,234 @@
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>Q3-R01</t>
+          <t>Q3-R04</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>Q2-016</t>
+          <t>Q2-018</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>leg2:descent</t>
+          <t>leg3:cruise</t>
         </is>
       </c>
       <c r="C181" s="4" t="n">
-        <v>1359.940291110606</v>
+        <v>5676.089369352236</v>
       </c>
       <c r="D181" s="4" t="n">
-        <v>1388.820027438731</v>
+        <v>6048.454050569748</v>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F181" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F181" s="3" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>Q2-016</t>
+          <t>Q2-018</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>S003:handover</t>
+          <t>leg3:descent</t>
         </is>
       </c>
       <c r="C182" s="4" t="n">
-        <v>1388.820027438731</v>
+        <v>6048.454050569748</v>
       </c>
       <c r="D182" s="4" t="n">
-        <v>1568.820027438731</v>
+        <v>6183.72363369963</v>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F182" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F182" s="3" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>Q2-016</t>
+          <t>Q2-019</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>leg3:climb</t>
+          <t>leg1:climb</t>
         </is>
       </c>
       <c r="C183" s="4" t="n">
-        <v>1568.820027438731</v>
+        <v>406.776</v>
       </c>
       <c r="D183" s="4" t="n">
-        <v>1643.254740166595</v>
+        <v>534.8670583496094</v>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F183" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F183" s="3" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>Q2-016</t>
+          <t>Q2-019</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>leg3:cruise</t>
+          <t>leg1:cruise</t>
         </is>
       </c>
       <c r="C184" s="4" t="n">
-        <v>1643.254740166595</v>
+        <v>534.8670583496094</v>
       </c>
       <c r="D184" s="4" t="n">
-        <v>1920.647011525587</v>
+        <v>797.5035140446726</v>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F184" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F184" s="3" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>Q2-016</t>
+          <t>Q2-019</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>leg3:cruise</t>
+          <t>leg1:cruise</t>
         </is>
       </c>
       <c r="C185" s="4" t="n">
-        <v>1920.647011525587</v>
+        <v>797.5035140446726</v>
       </c>
       <c r="D185" s="4" t="n">
-        <v>2248.519678212971</v>
+        <v>837.1644294706809</v>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F185" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F185" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>Q2-016</t>
+          <t>Q2-019</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>leg3:descent</t>
+          <t>leg1:descent</t>
         </is>
       </c>
       <c r="C186" s="4" t="n">
-        <v>2248.519678212971</v>
+        <v>837.1644294706809</v>
       </c>
       <c r="D186" s="4" t="n">
-        <v>2422.161333486408</v>
+        <v>902.5536994902122</v>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F186" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F186" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>Q2-017</t>
+          <t>Q2-019</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>leg1:climb</t>
+          <t>S007:handover</t>
         </is>
       </c>
       <c r="C187" s="4" t="n">
-        <v>480.495</v>
+        <v>902.5536994902122</v>
       </c>
       <c r="D187" s="4" t="n">
-        <v>552.9967016601563</v>
+        <v>1082.553699490212</v>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F187" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F187" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>Q2-017</t>
+          <t>Q2-019</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>leg1:cruise</t>
+          <t>leg2:climb</t>
         </is>
       </c>
       <c r="C188" s="4" t="n">
-        <v>552.9967016601563</v>
+        <v>1082.553699490212</v>
       </c>
       <c r="D188" s="4" t="n">
-        <v>816.5349540589515</v>
+        <v>1134.02643712042</v>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F188" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F188" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R01</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>Q2-017</t>
+          <t>Q2-019</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>leg1:cruise</t>
+          <t>leg2:cruise</t>
         </is>
       </c>
       <c r="C189" s="4" t="n">
-        <v>816.5349540589515</v>
+        <v>1134.02643712042</v>
       </c>
       <c r="D189" s="4" t="n">
-        <v>1001.442838832359</v>
+        <v>1281.983732581262</v>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
@@ -8444,19 +8372,19 @@
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>Q2-017</t>
+          <t>Q2-019</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>leg1:cruise</t>
+          <t>leg2:descent</t>
         </is>
       </c>
       <c r="C190" s="4" t="n">
-        <v>1001.442838832359</v>
+        <v>1281.983732581262</v>
       </c>
       <c r="D190" s="4" t="n">
-        <v>1047.084065332435</v>
+        <v>1293.351017737512</v>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
@@ -8465,26 +8393,26 @@
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R01</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>Q2-017</t>
+          <t>Q2-019</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>leg1:descent</t>
+          <t>S015:handover</t>
         </is>
       </c>
       <c r="C191" s="4" t="n">
-        <v>1047.084065332435</v>
+        <v>1293.351017737512</v>
       </c>
       <c r="D191" s="4" t="n">
-        <v>1091.81119240763</v>
+        <v>1473.351017737512</v>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
@@ -8493,26 +8421,26 @@
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R01</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>Q2-017</t>
+          <t>Q2-019</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>S002:handover</t>
+          <t>leg3:climb</t>
         </is>
       </c>
       <c r="C192" s="4" t="n">
-        <v>1091.81119240763</v>
+        <v>1473.351017737512</v>
       </c>
       <c r="D192" s="4" t="n">
-        <v>1451.81119240763</v>
+        <v>1505.78410286121</v>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
@@ -8521,26 +8449,26 @@
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R01</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>Q2-017</t>
+          <t>Q2-019</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>leg2:climb</t>
+          <t>leg3:cruise</t>
         </is>
       </c>
       <c r="C193" s="4" t="n">
-        <v>1451.81119240763</v>
+        <v>1505.78410286121</v>
       </c>
       <c r="D193" s="4" t="n">
-        <v>1487.592894067787</v>
+        <v>1644.178605690686</v>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
@@ -8549,82 +8477,74 @@
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R01</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>Q2-017</t>
+          <t>Q2-019</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>leg2:cruise</t>
+          <t>leg3:cruise</t>
         </is>
       </c>
       <c r="C194" s="4" t="n">
-        <v>1487.592894067787</v>
+        <v>1644.178605690686</v>
       </c>
       <c r="D194" s="4" t="n">
-        <v>1533.234120567862</v>
+        <v>1906.409634302563</v>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F194" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F194" s="3" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>Q2-017</t>
+          <t>Q2-019</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>leg2:cruise</t>
+          <t>leg3:descent</t>
         </is>
       </c>
       <c r="C195" s="4" t="n">
-        <v>1533.234120567862</v>
+        <v>1906.409634302563</v>
       </c>
       <c r="D195" s="4" t="n">
-        <v>1718.14200534127</v>
+        <v>2084.049336451001</v>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F195" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R01</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F195" s="3" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>Q2-017</t>
+          <t>Q2-020</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>leg2:cruise</t>
+          <t>leg1:climb</t>
         </is>
       </c>
       <c r="C196" s="4" t="n">
-        <v>1718.14200534127</v>
+        <v>1703.479</v>
       </c>
       <c r="D196" s="4" t="n">
-        <v>1981.680257740065</v>
+        <v>1858.228129231771</v>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
@@ -8636,19 +8556,19 @@
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>Q2-017</t>
+          <t>Q2-020</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>leg2:descent</t>
+          <t>leg1:cruise</t>
         </is>
       </c>
       <c r="C197" s="4" t="n">
-        <v>1981.680257740065</v>
+        <v>1858.228129231771</v>
       </c>
       <c r="D197" s="4" t="n">
-        <v>2072.307384815261</v>
+        <v>2185.831114642806</v>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
@@ -8660,67 +8580,75 @@
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>Q2-018</t>
+          <t>Q2-020</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>leg1:climb</t>
+          <t>leg1:cruise</t>
         </is>
       </c>
       <c r="C198" s="4" t="n">
-        <v>4122.85</v>
+        <v>2185.831114642806</v>
       </c>
       <c r="D198" s="4" t="n">
-        <v>4231.065666503907</v>
+        <v>2309.861617416199</v>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F198" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F198" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>Q2-018</t>
+          <t>Q2-020</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>leg1:cruise</t>
+          <t>leg1:descent</t>
         </is>
       </c>
       <c r="C199" s="4" t="n">
-        <v>4231.065666503907</v>
+        <v>2309.861617416199</v>
       </c>
       <c r="D199" s="4" t="n">
-        <v>4603.430347721419</v>
+        <v>2406.240572494324</v>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F199" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F199" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>Q2-018</t>
+          <t>Q2-020</t>
         </is>
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>leg1:cruise</t>
+          <t>S014:handover</t>
         </is>
       </c>
       <c r="C200" s="4" t="n">
-        <v>4603.430347721419</v>
+        <v>2406.240572494324</v>
       </c>
       <c r="D200" s="4" t="n">
-        <v>4745.378763111718</v>
+        <v>2586.240572494324</v>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
@@ -8729,26 +8657,26 @@
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>Q3-R03</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>Q2-018</t>
+          <t>Q2-020</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>leg1:descent</t>
+          <t>leg2:climb</t>
         </is>
       </c>
       <c r="C201" s="4" t="n">
-        <v>4745.378763111718</v>
+        <v>2586.240572494324</v>
       </c>
       <c r="D201" s="4" t="n">
-        <v>4830.348346241602</v>
+        <v>2675.429516993022</v>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
@@ -8757,26 +8685,26 @@
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>Q3-R03</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
         <is>
-          <t>Q2-018</t>
+          <t>Q2-020</t>
         </is>
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>S004:handover</t>
+          <t>leg2:cruise</t>
         </is>
       </c>
       <c r="C202" s="4" t="n">
-        <v>4830.348346241602</v>
+        <v>2675.429516993022</v>
       </c>
       <c r="D202" s="4" t="n">
-        <v>5118.348346241602</v>
+        <v>2812.049132622352</v>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
@@ -8785,222 +8713,194 @@
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>Q3-R03</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>Q2-018</t>
+          <t>Q2-020</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>leg2:climb</t>
+          <t>leg2:cruise</t>
         </is>
       </c>
       <c r="C203" s="4" t="n">
-        <v>5118.348346241602</v>
+        <v>2812.049132622352</v>
       </c>
       <c r="D203" s="4" t="n">
-        <v>5173.350978077539</v>
+        <v>3269.406107542496</v>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F203" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R03</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F203" s="3" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>Q2-018</t>
+          <t>Q2-020</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>leg2:cruise</t>
+          <t>leg2:descent</t>
         </is>
       </c>
       <c r="C204" s="4" t="n">
-        <v>5173.350978077539</v>
+        <v>3269.406107542496</v>
       </c>
       <c r="D204" s="4" t="n">
-        <v>5178.351</v>
+        <v>3431.992840940934</v>
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F204" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R03</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F204" s="3" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>Q2-018</t>
+          <t>Q2-020</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>leg2:cruise</t>
+          <t>S011:handover</t>
         </is>
       </c>
       <c r="C205" s="4" t="n">
-        <v>5178.351</v>
+        <v>3431.992840940934</v>
       </c>
       <c r="D205" s="4" t="n">
-        <v>5347.227081641819</v>
+        <v>3641.992840940934</v>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F205" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R04</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F205" s="3" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
         <is>
-          <t>Q2-018</t>
+          <t>Q2-020</t>
         </is>
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t>leg2:descent</t>
+          <t>leg3:climb</t>
         </is>
       </c>
       <c r="C206" s="4" t="n">
-        <v>5347.227081641819</v>
+        <v>3641.992840940934</v>
       </c>
       <c r="D206" s="4" t="n">
-        <v>5432.63037143674</v>
+        <v>3669.746759397965</v>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F206" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R04</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F206" s="3" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>Q2-018</t>
+          <t>Q2-020</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>S005:handover</t>
+          <t>leg3:cruise</t>
         </is>
       </c>
       <c r="C207" s="4" t="n">
-        <v>5432.63037143674</v>
+        <v>3669.746759397965</v>
       </c>
       <c r="D207" s="4" t="n">
-        <v>5720.63037143674</v>
+        <v>3903.752945454769</v>
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F207" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R04</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F207" s="3" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>Q2-018</t>
+          <t>Q2-020</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>leg3:climb</t>
+          <t>leg3:descent</t>
         </is>
       </c>
       <c r="C208" s="4" t="n">
-        <v>5720.63037143674</v>
+        <v>3903.752945454769</v>
       </c>
       <c r="D208" s="4" t="n">
-        <v>5773.194726905491</v>
+        <v>3970.817647603206</v>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F208" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R04</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F208" s="3" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>Q2-018</t>
+          <t>Q2-021</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>leg3:cruise</t>
+          <t>leg1:climb</t>
         </is>
       </c>
       <c r="C209" s="4" t="n">
-        <v>5773.194726905491</v>
+        <v>2010.17</v>
       </c>
       <c r="D209" s="4" t="n">
-        <v>5861.735776503522</v>
+        <v>2082.671701660156</v>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F209" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R04</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F209" s="3" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
         <is>
-          <t>Q2-018</t>
+          <t>Q2-021</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>leg3:cruise</t>
+          <t>leg1:cruise</t>
         </is>
       </c>
       <c r="C210" s="4" t="n">
-        <v>5861.735776503522</v>
+        <v>2082.671701660156</v>
       </c>
       <c r="D210" s="4" t="n">
-        <v>6125.235189363694</v>
+        <v>2346.209954058952</v>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
@@ -9012,91 +8912,103 @@
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>Q2-018</t>
+          <t>Q2-021</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>leg3:descent</t>
+          <t>leg1:cruise</t>
         </is>
       </c>
       <c r="C211" s="4" t="n">
-        <v>6125.235189363694</v>
+        <v>2346.209954058952</v>
       </c>
       <c r="D211" s="4" t="n">
-        <v>6224.590633699631</v>
+        <v>2576.759065332436</v>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F211" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F211" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>Q2-019</t>
+          <t>Q2-021</t>
         </is>
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>leg1:climb</t>
+          <t>leg1:descent</t>
         </is>
       </c>
       <c r="C212" s="4" t="n">
-        <v>5803.594</v>
+        <v>2576.759065332436</v>
       </c>
       <c r="D212" s="4" t="n">
-        <v>5885.330444091797</v>
+        <v>2621.486192407631</v>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F212" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F212" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>Q2-019</t>
+          <t>Q2-021</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>leg1:cruise</t>
+          <t>S002:handover</t>
         </is>
       </c>
       <c r="C213" s="4" t="n">
-        <v>5885.330444091797</v>
+        <v>2621.486192407631</v>
       </c>
       <c r="D213" s="4" t="n">
-        <v>6175.688269872389</v>
+        <v>2981.486192407631</v>
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F213" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F213" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
         <is>
-          <t>Q2-019</t>
+          <t>Q2-021</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>leg1:cruise</t>
+          <t>leg2:climb</t>
         </is>
       </c>
       <c r="C214" s="4" t="n">
-        <v>6175.688269872389</v>
+        <v>2981.486192407631</v>
       </c>
       <c r="D214" s="4" t="n">
-        <v>6423.932651586676</v>
+        <v>3017.267894067787</v>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
@@ -9105,26 +9017,26 @@
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>Q3-R04</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>Q2-019</t>
+          <t>Q2-021</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>leg1:descent</t>
+          <t>leg2:cruise</t>
         </is>
       </c>
       <c r="C215" s="4" t="n">
-        <v>6423.932651586676</v>
+        <v>3017.267894067787</v>
       </c>
       <c r="D215" s="4" t="n">
-        <v>6464.736384496832</v>
+        <v>3247.81700534127</v>
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
@@ -9133,138 +9045,122 @@
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>Q3-R04</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>Q2-019</t>
+          <t>Q2-021</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>S008:handover</t>
+          <t>leg2:cruise</t>
         </is>
       </c>
       <c r="C216" s="4" t="n">
-        <v>6464.736384496832</v>
+        <v>3247.81700534127</v>
       </c>
       <c r="D216" s="4" t="n">
-        <v>6674.736384496832</v>
+        <v>3511.355257740066</v>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F216" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R04</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F216" s="3" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>Q2-019</t>
+          <t>Q2-021</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>leg2:climb</t>
+          <t>leg2:descent</t>
         </is>
       </c>
       <c r="C217" s="4" t="n">
-        <v>6674.736384496832</v>
+        <v>3511.355257740066</v>
       </c>
       <c r="D217" s="4" t="n">
-        <v>6708.739495255296</v>
+        <v>3601.982384815261</v>
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F217" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R04</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F217" s="3" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
         <is>
-          <t>Q2-019</t>
+          <t>Q2-022</t>
         </is>
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>leg2:cruise</t>
+          <t>leg1:climb</t>
         </is>
       </c>
       <c r="C218" s="4" t="n">
-        <v>6708.739495255296</v>
+        <v>540</v>
       </c>
       <c r="D218" s="4" t="n">
-        <v>6787.068</v>
+        <v>598.1426440429688</v>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F218" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R04</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F218" s="3" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>Q2-019</t>
+          <t>Q2-022</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>leg2:cruise</t>
+          <t>leg1:cruise</t>
         </is>
       </c>
       <c r="C219" s="4" t="n">
-        <v>6787.068</v>
+        <v>598.1426440429688</v>
       </c>
       <c r="D219" s="4" t="n">
-        <v>6956.983876969583</v>
+        <v>801.7412336108687</v>
       </c>
       <c r="E219" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F219" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R05</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F219" s="3" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>Q2-019</t>
+          <t>Q2-022</t>
         </is>
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>leg2:cruise</t>
+          <t>leg1:descent</t>
         </is>
       </c>
       <c r="C220" s="4" t="n">
-        <v>6956.983876969583</v>
+        <v>801.7412336108687</v>
       </c>
       <c r="D220" s="4" t="n">
-        <v>7247.341702750175</v>
+        <v>846.2695386645796</v>
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
@@ -9276,19 +9172,19 @@
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>Q2-019</t>
+          <t>Q2-022</t>
         </is>
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>leg2:descent</t>
+          <t>S001:handover</t>
         </is>
       </c>
       <c r="C221" s="4" t="n">
-        <v>7247.341702750175</v>
+        <v>846.2695386645796</v>
       </c>
       <c r="D221" s="4" t="n">
-        <v>7345.425435660331</v>
+        <v>1314.26953866458</v>
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
@@ -9300,19 +9196,19 @@
     <row r="222">
       <c r="A222" s="4" t="inlineStr">
         <is>
-          <t>Q2-020</t>
+          <t>Q2-022</t>
         </is>
       </c>
       <c r="B222" s="4" t="inlineStr">
         <is>
-          <t>leg1:climb</t>
+          <t>leg2:climb</t>
         </is>
       </c>
       <c r="C222" s="4" t="n">
-        <v>2001.642</v>
+        <v>1314.26953866458</v>
       </c>
       <c r="D222" s="4" t="n">
-        <v>2081.107946451823</v>
+        <v>1349.892182707548</v>
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
@@ -9324,19 +9220,19 @@
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
         <is>
-          <t>Q2-020</t>
+          <t>Q2-022</t>
         </is>
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>leg1:cruise</t>
+          <t>leg2:cruise</t>
         </is>
       </c>
       <c r="C223" s="4" t="n">
-        <v>2081.107946451823</v>
+        <v>1349.892182707548</v>
       </c>
       <c r="D223" s="4" t="n">
-        <v>2293.521825012733</v>
+        <v>1553.490772275448</v>
       </c>
       <c r="E223" s="3" t="inlineStr">
         <is>
@@ -9348,19 +9244,19 @@
     <row r="224">
       <c r="A224" s="4" t="inlineStr">
         <is>
-          <t>Q2-020</t>
+          <t>Q2-022</t>
         </is>
       </c>
       <c r="B224" s="4" t="inlineStr">
         <is>
-          <t>leg1:descent</t>
+          <t>leg2:descent</t>
         </is>
       </c>
       <c r="C224" s="4" t="n">
-        <v>2293.521825012733</v>
+        <v>1553.490772275448</v>
       </c>
       <c r="D224" s="4" t="n">
-        <v>2314.040960754921</v>
+        <v>1626.169077329159</v>
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
@@ -9372,19 +9268,19 @@
     <row r="225">
       <c r="A225" s="4" t="inlineStr">
         <is>
-          <t>Q2-020</t>
+          <t>Q2-023</t>
         </is>
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>S006:handover</t>
+          <t>leg1:climb</t>
         </is>
       </c>
       <c r="C225" s="4" t="n">
-        <v>2314.040960754921</v>
+        <v>3564.897</v>
       </c>
       <c r="D225" s="4" t="n">
-        <v>2524.040960754921</v>
+        <v>3620.073304117839</v>
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
@@ -9396,19 +9292,19 @@
     <row r="226">
       <c r="A226" s="4" t="inlineStr">
         <is>
-          <t>Q2-020</t>
+          <t>Q2-023</t>
         </is>
       </c>
       <c r="B226" s="4" t="inlineStr">
         <is>
-          <t>leg2:climb</t>
+          <t>leg1:cruise</t>
         </is>
       </c>
       <c r="C226" s="4" t="n">
-        <v>2524.040960754921</v>
+        <v>3620.073304117839</v>
       </c>
       <c r="D226" s="4" t="n">
-        <v>2541.140240540077</v>
+        <v>3949.523928911089</v>
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
@@ -9420,115 +9316,131 @@
     <row r="227">
       <c r="A227" s="4" t="inlineStr">
         <is>
-          <t>Q2-020</t>
+          <t>Q2-023</t>
         </is>
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>leg2:cruise</t>
+          <t>leg1:cruise</t>
         </is>
       </c>
       <c r="C227" s="4" t="n">
-        <v>2541.140240540077</v>
+        <v>3949.523928911089</v>
       </c>
       <c r="D227" s="4" t="n">
-        <v>2753.554119100987</v>
+        <v>4095.502050974259</v>
       </c>
       <c r="E227" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F227" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F227" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R03</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="4" t="inlineStr">
         <is>
-          <t>Q2-020</t>
+          <t>Q2-023</t>
         </is>
       </c>
       <c r="B228" s="4" t="inlineStr">
         <is>
-          <t>leg2:descent</t>
+          <t>leg1:descent</t>
         </is>
       </c>
       <c r="C228" s="4" t="n">
-        <v>2753.554119100987</v>
+        <v>4095.502050974259</v>
       </c>
       <c r="D228" s="4" t="n">
-        <v>2848.913254843175</v>
+        <v>4120.793615915665</v>
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F228" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F228" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R03</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="4" t="inlineStr">
         <is>
-          <t>Q2-021</t>
+          <t>Q2-023</t>
         </is>
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>leg1:climb</t>
+          <t>S009:handover</t>
         </is>
       </c>
       <c r="C229" s="4" t="n">
-        <v>5010.417</v>
+        <v>4120.793615915665</v>
       </c>
       <c r="D229" s="4" t="n">
-        <v>5184.058655273438</v>
+        <v>4300.793615915665</v>
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F229" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F229" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R03</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="4" t="inlineStr">
         <is>
-          <t>Q2-021</t>
+          <t>Q2-023</t>
         </is>
       </c>
       <c r="B230" s="4" t="inlineStr">
         <is>
-          <t>leg1:cruise</t>
+          <t>leg2:climb</t>
         </is>
       </c>
       <c r="C230" s="4" t="n">
-        <v>5184.058655273438</v>
+        <v>4300.793615915665</v>
       </c>
       <c r="D230" s="4" t="n">
-        <v>5446.350544275052</v>
+        <v>4345.314683217098</v>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F230" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F230" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R03</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>Q2-021</t>
+          <t>Q2-023</t>
         </is>
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>leg1:cruise</t>
+          <t>leg2:cruise</t>
         </is>
       </c>
       <c r="C231" s="4" t="n">
-        <v>5446.350544275052</v>
+        <v>4345.314683217098</v>
       </c>
       <c r="D231" s="4" t="n">
-        <v>5668.270605710538</v>
+        <v>4566.141561283164</v>
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
@@ -9537,26 +9449,26 @@
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>Q3-R04</t>
+          <t>Q3-R03</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="4" t="inlineStr">
         <is>
-          <t>Q2-021</t>
+          <t>Q2-023</t>
         </is>
       </c>
       <c r="B232" s="4" t="inlineStr">
         <is>
-          <t>leg1:descent</t>
+          <t>leg2:descent</t>
         </is>
       </c>
       <c r="C232" s="4" t="n">
-        <v>5668.270605710538</v>
+        <v>4566.141561283164</v>
       </c>
       <c r="D232" s="4" t="n">
-        <v>5779.922674802335</v>
+        <v>4633.566842044883</v>
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
@@ -9565,26 +9477,26 @@
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>Q3-R04</t>
+          <t>Q3-R03</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="4" t="inlineStr">
         <is>
-          <t>Q2-021</t>
+          <t>Q2-023</t>
         </is>
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>S003:handover</t>
+          <t>S005:handover</t>
         </is>
       </c>
       <c r="C233" s="4" t="n">
-        <v>5779.922674802335</v>
+        <v>4633.566842044883</v>
       </c>
       <c r="D233" s="4" t="n">
-        <v>6175.922674802335</v>
+        <v>4843.566842044883</v>
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
@@ -9593,26 +9505,26 @@
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>Q3-R04</t>
+          <t>Q3-R03</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="4" t="inlineStr">
         <is>
-          <t>Q2-021</t>
+          <t>Q2-023</t>
         </is>
       </c>
       <c r="B234" s="4" t="inlineStr">
         <is>
-          <t>leg2:climb</t>
+          <t>leg3:climb</t>
         </is>
       </c>
       <c r="C234" s="4" t="n">
-        <v>6175.922674802335</v>
+        <v>4843.566842044883</v>
       </c>
       <c r="D234" s="4" t="n">
-        <v>6265.244330075772</v>
+        <v>4887.370471602175</v>
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
@@ -9621,26 +9533,26 @@
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>Q3-R04</t>
+          <t>Q3-R03</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="4" t="inlineStr">
         <is>
-          <t>Q2-021</t>
+          <t>Q2-023</t>
         </is>
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>leg2:cruise</t>
+          <t>leg3:cruise</t>
         </is>
       </c>
       <c r="C235" s="4" t="n">
-        <v>6265.244330075772</v>
+        <v>4887.370471602175</v>
       </c>
       <c r="D235" s="4" t="n">
-        <v>6487.164391511258</v>
+        <v>4998.070304700545</v>
       </c>
       <c r="E235" s="3" t="inlineStr">
         <is>
@@ -9649,26 +9561,26 @@
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>Q3-R04</t>
+          <t>Q3-R03</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="4" t="inlineStr">
         <is>
-          <t>Q2-021</t>
+          <t>Q2-023</t>
         </is>
       </c>
       <c r="B236" s="4" t="inlineStr">
         <is>
-          <t>leg2:cruise</t>
+          <t>leg3:cruise</t>
         </is>
       </c>
       <c r="C236" s="4" t="n">
-        <v>6487.164391511258</v>
+        <v>4998.070304700545</v>
       </c>
       <c r="D236" s="4" t="n">
-        <v>6749.456280512873</v>
+        <v>5327.421049674928</v>
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
@@ -9680,19 +9592,19 @@
     <row r="237">
       <c r="A237" s="4" t="inlineStr">
         <is>
-          <t>Q2-021</t>
+          <t>Q2-023</t>
         </is>
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>leg2:descent</t>
+          <t>leg3:descent</t>
         </is>
       </c>
       <c r="C237" s="4" t="n">
-        <v>6749.456280512873</v>
+        <v>5327.421049674928</v>
       </c>
       <c r="D237" s="4" t="n">
-        <v>6966.508349604669</v>
+        <v>5406.905405143679</v>
       </c>
       <c r="E237" s="3" t="inlineStr">
         <is>
@@ -9704,7 +9616,7 @@
     <row r="238">
       <c r="A238" s="4" t="inlineStr">
         <is>
-          <t>Q2-022</t>
+          <t>Q2-024</t>
         </is>
       </c>
       <c r="B238" s="4" t="inlineStr">
@@ -9713,10 +9625,10 @@
         </is>
       </c>
       <c r="C238" s="4" t="n">
-        <v>4436.107</v>
+        <v>422.844</v>
       </c>
       <c r="D238" s="4" t="n">
-        <v>4515.572946451823</v>
+        <v>513.3379412434896</v>
       </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
@@ -9728,7 +9640,7 @@
     <row r="239">
       <c r="A239" s="4" t="inlineStr">
         <is>
-          <t>Q2-022</t>
+          <t>Q2-024</t>
         </is>
       </c>
       <c r="B239" s="4" t="inlineStr">
@@ -9737,10 +9649,10 @@
         </is>
       </c>
       <c r="C239" s="4" t="n">
-        <v>4515.572946451823</v>
+        <v>513.3379412434896</v>
       </c>
       <c r="D239" s="4" t="n">
-        <v>4727.986825012733</v>
+        <v>842.3436921002185</v>
       </c>
       <c r="E239" s="3" t="inlineStr">
         <is>
@@ -9752,187 +9664,215 @@
     <row r="240">
       <c r="A240" s="4" t="inlineStr">
         <is>
-          <t>Q2-022</t>
+          <t>Q2-024</t>
         </is>
       </c>
       <c r="B240" s="4" t="inlineStr">
         <is>
-          <t>leg1:descent</t>
+          <t>leg1:cruise</t>
         </is>
       </c>
       <c r="C240" s="4" t="n">
-        <v>4727.986825012733</v>
+        <v>842.3436921002185</v>
       </c>
       <c r="D240" s="4" t="n">
-        <v>4748.50596075492</v>
+        <v>917.4414726793655</v>
       </c>
       <c r="E240" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F240" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F240" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="4" t="inlineStr">
         <is>
-          <t>Q2-022</t>
+          <t>Q2-024</t>
         </is>
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>S006:handover</t>
+          <t>leg1:descent</t>
         </is>
       </c>
       <c r="C241" s="4" t="n">
-        <v>4748.50596075492</v>
+        <v>917.4414726793655</v>
       </c>
       <c r="D241" s="4" t="n">
-        <v>4958.50596075492</v>
+        <v>936.434202171553</v>
       </c>
       <c r="E241" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F241" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F241" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="4" t="inlineStr">
         <is>
-          <t>Q2-022</t>
+          <t>Q2-024</t>
         </is>
       </c>
       <c r="B242" s="4" t="inlineStr">
         <is>
-          <t>leg2:climb</t>
+          <t>S013:handover</t>
         </is>
       </c>
       <c r="C242" s="4" t="n">
-        <v>4958.50596075492</v>
+        <v>936.434202171553</v>
       </c>
       <c r="D242" s="4" t="n">
-        <v>4975.605240540076</v>
+        <v>1116.434202171553</v>
       </c>
       <c r="E242" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F242" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F242" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="4" t="inlineStr">
         <is>
-          <t>Q2-022</t>
+          <t>Q2-024</t>
         </is>
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>leg2:cruise</t>
+          <t>leg2:climb</t>
         </is>
       </c>
       <c r="C243" s="4" t="n">
-        <v>4975.605240540076</v>
+        <v>1116.434202171553</v>
       </c>
       <c r="D243" s="4" t="n">
-        <v>5188.019119100986</v>
+        <v>1167.224326683272</v>
       </c>
       <c r="E243" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F243" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F243" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="4" t="inlineStr">
         <is>
-          <t>Q2-022</t>
+          <t>Q2-024</t>
         </is>
       </c>
       <c r="B244" s="4" t="inlineStr">
         <is>
-          <t>leg2:descent</t>
+          <t>leg2:cruise</t>
         </is>
       </c>
       <c r="C244" s="4" t="n">
-        <v>5188.019119100986</v>
+        <v>1167.224326683272</v>
       </c>
       <c r="D244" s="4" t="n">
-        <v>5283.378254843174</v>
+        <v>1282.113707487873</v>
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F244" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F244" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="4" t="inlineStr">
         <is>
-          <t>Q2-023</t>
+          <t>Q2-024</t>
         </is>
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>leg1:climb</t>
+          <t>leg2:descent</t>
         </is>
       </c>
       <c r="C245" s="4" t="n">
-        <v>3537.613</v>
+        <v>1282.113707487873</v>
       </c>
       <c r="D245" s="4" t="n">
-        <v>3603.849962890625</v>
+        <v>1343.101856901935</v>
       </c>
       <c r="E245" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F245" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F245" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="4" t="inlineStr">
         <is>
-          <t>Q2-023</t>
+          <t>Q2-024</t>
         </is>
       </c>
       <c r="B246" s="4" t="inlineStr">
         <is>
-          <t>leg1:cruise</t>
+          <t>S010:handover</t>
         </is>
       </c>
       <c r="C246" s="4" t="n">
-        <v>3603.849962890625</v>
+        <v>1343.101856901935</v>
       </c>
       <c r="D246" s="4" t="n">
-        <v>3933.200707865008</v>
+        <v>1553.101856901935</v>
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F246" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F246" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="4" t="inlineStr">
         <is>
-          <t>Q2-023</t>
+          <t>Q2-024</t>
         </is>
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>leg1:cruise</t>
+          <t>leg3:climb</t>
         </is>
       </c>
       <c r="C247" s="4" t="n">
-        <v>3933.200707865008</v>
+        <v>1553.101856901935</v>
       </c>
       <c r="D247" s="4" t="n">
-        <v>4043.900540963378</v>
+        <v>1581.114035450112</v>
       </c>
       <c r="E247" s="3" t="inlineStr">
         <is>
@@ -9941,26 +9881,26 @@
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
-          <t>Q3-R03</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="4" t="inlineStr">
         <is>
-          <t>Q2-023</t>
+          <t>Q2-024</t>
         </is>
       </c>
       <c r="B248" s="4" t="inlineStr">
         <is>
-          <t>leg1:descent</t>
+          <t>leg3:cruise</t>
         </is>
       </c>
       <c r="C248" s="4" t="n">
-        <v>4043.900540963378</v>
+        <v>1581.114035450112</v>
       </c>
       <c r="D248" s="4" t="n">
-        <v>4096.464896432129</v>
+        <v>1651.012905507105</v>
       </c>
       <c r="E248" s="3" t="inlineStr">
         <is>
@@ -9969,138 +9909,122 @@
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>Q3-R03</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
         <is>
-          <t>Q2-023</t>
+          <t>Q2-024</t>
         </is>
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>S005:handover</t>
+          <t>leg3:cruise</t>
         </is>
       </c>
       <c r="C249" s="4" t="n">
-        <v>4096.464896432129</v>
+        <v>1651.012905507105</v>
       </c>
       <c r="D249" s="4" t="n">
-        <v>4276.464896432129</v>
+        <v>1979.821939753748</v>
       </c>
       <c r="E249" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F249" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R03</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F249" s="3" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="4" t="inlineStr">
         <is>
-          <t>Q2-023</t>
+          <t>Q2-024</t>
         </is>
       </c>
       <c r="B250" s="4" t="inlineStr">
         <is>
-          <t>leg2:climb</t>
+          <t>leg3:descent</t>
         </is>
       </c>
       <c r="C250" s="4" t="n">
-        <v>4276.464896432129</v>
+        <v>1979.821939753748</v>
       </c>
       <c r="D250" s="4" t="n">
-        <v>4332.652630400227</v>
+        <v>2102.99655401156</v>
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F250" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R03</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F250" s="3" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="4" t="inlineStr">
         <is>
-          <t>Q2-023</t>
+          <t>Q2-025</t>
         </is>
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>leg2:cruise</t>
+          <t>leg1:climb</t>
         </is>
       </c>
       <c r="C251" s="4" t="n">
-        <v>4332.652630400227</v>
+        <v>2235.961</v>
       </c>
       <c r="D251" s="4" t="n">
-        <v>4553.479508466294</v>
+        <v>2344.553729492188</v>
       </c>
       <c r="E251" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F251" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R03</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F251" s="3" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="4" t="inlineStr">
         <is>
-          <t>Q2-023</t>
+          <t>Q2-025</t>
         </is>
       </c>
       <c r="B252" s="4" t="inlineStr">
         <is>
-          <t>leg2:descent</t>
+          <t>leg1:cruise</t>
         </is>
       </c>
       <c r="C252" s="4" t="n">
-        <v>4553.479508466294</v>
+        <v>2344.553729492188</v>
       </c>
       <c r="D252" s="4" t="n">
-        <v>4606.904789228012</v>
+        <v>2607.783147303084</v>
       </c>
       <c r="E252" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F252" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R03</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F252" s="3" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
         <is>
-          <t>Q2-023</t>
+          <t>Q2-025</t>
         </is>
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>S009:handover</t>
+          <t>leg1:cruise</t>
         </is>
       </c>
       <c r="C253" s="4" t="n">
-        <v>4606.904789228012</v>
+        <v>2607.783147303084</v>
       </c>
       <c r="D253" s="4" t="n">
-        <v>4786.904789228012</v>
+        <v>2667.836554640889</v>
       </c>
       <c r="E253" s="3" t="inlineStr">
         <is>
@@ -10109,26 +10033,26 @@
       </c>
       <c r="F253" s="3" t="inlineStr">
         <is>
-          <t>Q3-R03</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="4" t="inlineStr">
         <is>
-          <t>Q2-023</t>
+          <t>Q2-025</t>
         </is>
       </c>
       <c r="B254" s="4" t="inlineStr">
         <is>
-          <t>leg3:climb</t>
+          <t>leg1:descent</t>
         </is>
       </c>
       <c r="C254" s="4" t="n">
-        <v>4786.904789228012</v>
+        <v>2667.836554640889</v>
       </c>
       <c r="D254" s="4" t="n">
-        <v>4807.981093345851</v>
+        <v>2691.577466506123</v>
       </c>
       <c r="E254" s="3" t="inlineStr">
         <is>
@@ -10137,26 +10061,26 @@
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
-          <t>Q3-R03</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
         <is>
-          <t>Q2-023</t>
+          <t>Q2-025</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>leg3:cruise</t>
+          <t>S013:handover</t>
         </is>
       </c>
       <c r="C255" s="4" t="n">
-        <v>4807.981093345851</v>
+        <v>2691.577466506123</v>
       </c>
       <c r="D255" s="4" t="n">
-        <v>4953.959215409021</v>
+        <v>2907.577466506123</v>
       </c>
       <c r="E255" s="3" t="inlineStr">
         <is>
@@ -10165,194 +10089,222 @@
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
-          <t>Q3-R03</t>
+          <t>Q3-R02</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="4" t="inlineStr">
         <is>
-          <t>Q2-023</t>
+          <t>Q2-025</t>
         </is>
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>leg3:cruise</t>
+          <t>leg2:climb</t>
         </is>
       </c>
       <c r="C256" s="4" t="n">
-        <v>4953.959215409021</v>
+        <v>2907.577466506123</v>
       </c>
       <c r="D256" s="4" t="n">
-        <v>5283.409840202271</v>
+        <v>2941.508013381123</v>
       </c>
       <c r="E256" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F256" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F256" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
         <is>
-          <t>Q2-023</t>
+          <t>Q2-025</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>leg3:descent</t>
+          <t>leg2:cruise</t>
         </is>
       </c>
       <c r="C257" s="4" t="n">
-        <v>5283.409840202271</v>
+        <v>2941.508013381123</v>
       </c>
       <c r="D257" s="4" t="n">
-        <v>5349.621405143677</v>
+        <v>3131.85600569727</v>
       </c>
       <c r="E257" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F257" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F257" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="4" t="inlineStr">
         <is>
-          <t>Q2-024</t>
+          <t>Q2-025</t>
         </is>
       </c>
       <c r="B258" s="4" t="inlineStr">
         <is>
-          <t>leg1:climb</t>
+          <t>leg2:descent</t>
         </is>
       </c>
       <c r="C258" s="4" t="n">
-        <v>540</v>
+        <v>3131.85600569727</v>
       </c>
       <c r="D258" s="4" t="n">
-        <v>598.1426440429688</v>
+        <v>3210.21918929102</v>
       </c>
       <c r="E258" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F258" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F258" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
-          <t>Q2-024</t>
+          <t>Q2-025</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>leg1:cruise</t>
+          <t>S012:handover</t>
         </is>
       </c>
       <c r="C259" s="4" t="n">
-        <v>598.1426440429688</v>
+        <v>3210.21918929102</v>
       </c>
       <c r="D259" s="4" t="n">
-        <v>801.7412336108687</v>
+        <v>3498.21918929102</v>
       </c>
       <c r="E259" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F259" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F259" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="4" t="inlineStr">
         <is>
-          <t>Q2-024</t>
+          <t>Q2-025</t>
         </is>
       </c>
       <c r="B260" s="4" t="inlineStr">
         <is>
-          <t>leg1:descent</t>
+          <t>leg3:climb</t>
         </is>
       </c>
       <c r="C260" s="4" t="n">
-        <v>801.7412336108687</v>
+        <v>3498.21918929102</v>
       </c>
       <c r="D260" s="4" t="n">
-        <v>846.2695386645796</v>
+        <v>3546.62</v>
       </c>
       <c r="E260" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F260" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F260" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R02</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
         <is>
-          <t>Q2-024</t>
+          <t>Q2-025</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>S001:handover</t>
+          <t>leg3:climb</t>
         </is>
       </c>
       <c r="C261" s="4" t="n">
-        <v>846.2695386645796</v>
+        <v>3546.62</v>
       </c>
       <c r="D261" s="4" t="n">
-        <v>1314.26953866458</v>
+        <v>3551.619587240239</v>
       </c>
       <c r="E261" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F261" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F261" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R03</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="4" t="inlineStr">
         <is>
-          <t>Q2-024</t>
+          <t>Q2-025</t>
         </is>
       </c>
       <c r="B262" s="4" t="inlineStr">
         <is>
-          <t>leg2:climb</t>
+          <t>leg3:cruise</t>
         </is>
       </c>
       <c r="C262" s="4" t="n">
-        <v>1314.26953866458</v>
+        <v>3551.619587240239</v>
       </c>
       <c r="D262" s="4" t="n">
-        <v>1349.892182707548</v>
+        <v>3781.158535035518</v>
       </c>
       <c r="E262" s="3" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F262" s="3" t="n"/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F262" s="3" t="inlineStr">
+        <is>
+          <t>Q3-R03</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="4" t="inlineStr">
         <is>
-          <t>Q2-024</t>
+          <t>Q2-025</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>leg2:cruise</t>
+          <t>leg3:cruise</t>
         </is>
       </c>
       <c r="C263" s="4" t="n">
-        <v>1349.892182707548</v>
+        <v>3781.158535035518</v>
       </c>
       <c r="D263" s="4" t="n">
-        <v>1553.490772275448</v>
+        <v>4044.319033038763</v>
       </c>
       <c r="E263" s="3" t="inlineStr">
         <is>
@@ -10364,19 +10316,19 @@
     <row r="264">
       <c r="A264" s="4" t="inlineStr">
         <is>
-          <t>Q2-024</t>
+          <t>Q2-025</t>
         </is>
       </c>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>leg2:descent</t>
+          <t>leg3:descent</t>
         </is>
       </c>
       <c r="C264" s="4" t="n">
-        <v>1553.490772275448</v>
+        <v>4044.319033038763</v>
       </c>
       <c r="D264" s="4" t="n">
-        <v>1626.169077329159</v>
+        <v>4187.119530475286</v>
       </c>
       <c r="E264" s="3" t="inlineStr">
         <is>
@@ -10388,7 +10340,7 @@
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>Q2-025</t>
+          <t>Q2-026</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
@@ -10397,10 +10349,10 @@
         </is>
       </c>
       <c r="C265" s="4" t="n">
-        <v>2046.17</v>
+        <v>406.776</v>
       </c>
       <c r="D265" s="4" t="n">
-        <v>2160.410397949219</v>
+        <v>534.8670583496094</v>
       </c>
       <c r="E265" s="3" t="inlineStr">
         <is>
@@ -10412,7 +10364,7 @@
     <row r="266">
       <c r="A266" s="4" t="inlineStr">
         <is>
-          <t>Q2-025</t>
+          <t>Q2-026</t>
         </is>
       </c>
       <c r="B266" s="4" t="inlineStr">
@@ -10421,10 +10373,10 @@
         </is>
       </c>
       <c r="C266" s="4" t="n">
-        <v>2160.410397949219</v>
+        <v>534.8670583496094</v>
       </c>
       <c r="D266" s="4" t="n">
-        <v>2423.570895952465</v>
+        <v>797.5035140446726</v>
       </c>
       <c r="E266" s="3" t="inlineStr">
         <is>
@@ -10436,7 +10388,7 @@
     <row r="267">
       <c r="A267" s="4" t="inlineStr">
         <is>
-          <t>Q2-025</t>
+          <t>Q2-026</t>
         </is>
       </c>
       <c r="B267" s="4" t="inlineStr">
@@ -10445,10 +10397,10 @@
         </is>
       </c>
       <c r="C267" s="4" t="n">
-        <v>2423.570895952465</v>
+        <v>797.5035140446726</v>
       </c>
       <c r="D267" s="4" t="n">
-        <v>2653.109843747744</v>
+        <v>837.1644294706809</v>
       </c>
       <c r="E267" s="3" t="inlineStr">
         <is>
@@ -10457,14 +10409,14 @@
       </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R01</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="4" t="inlineStr">
         <is>
-          <t>Q2-025</t>
+          <t>Q2-026</t>
         </is>
       </c>
       <c r="B268" s="4" t="inlineStr">
@@ -10473,10 +10425,10 @@
         </is>
       </c>
       <c r="C268" s="4" t="n">
-        <v>2653.109843747744</v>
+        <v>837.1644294706809</v>
       </c>
       <c r="D268" s="4" t="n">
-        <v>2719.860341184267</v>
+        <v>902.5536994902122</v>
       </c>
       <c r="E268" s="3" t="inlineStr">
         <is>
@@ -10485,26 +10437,26 @@
       </c>
       <c r="F268" s="3" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R01</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="4" t="inlineStr">
         <is>
-          <t>Q2-025</t>
+          <t>Q2-026</t>
         </is>
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>S012:handover</t>
+          <t>S007:handover</t>
         </is>
       </c>
       <c r="C269" s="4" t="n">
-        <v>2719.860341184267</v>
+        <v>902.5536994902122</v>
       </c>
       <c r="D269" s="4" t="n">
-        <v>3007.860341184267</v>
+        <v>1112.553699490212</v>
       </c>
       <c r="E269" s="3" t="inlineStr">
         <is>
@@ -10513,14 +10465,14 @@
       </c>
       <c r="F269" s="3" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R01</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="4" t="inlineStr">
         <is>
-          <t>Q2-025</t>
+          <t>Q2-026</t>
         </is>
       </c>
       <c r="B270" s="4" t="inlineStr">
@@ -10529,10 +10481,10 @@
         </is>
       </c>
       <c r="C270" s="4" t="n">
-        <v>3007.860341184267</v>
+        <v>1112.553699490212</v>
       </c>
       <c r="D270" s="4" t="n">
-        <v>3070.550888059267</v>
+        <v>1167.044757839822</v>
       </c>
       <c r="E270" s="3" t="inlineStr">
         <is>
@@ -10541,14 +10493,14 @@
       </c>
       <c r="F270" s="3" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R01</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="4" t="inlineStr">
         <is>
-          <t>Q2-025</t>
+          <t>Q2-026</t>
         </is>
       </c>
       <c r="B271" s="4" t="inlineStr">
@@ -10557,10 +10509,10 @@
         </is>
       </c>
       <c r="C271" s="4" t="n">
-        <v>3070.550888059267</v>
+        <v>1167.044757839822</v>
       </c>
       <c r="D271" s="4" t="n">
-        <v>3260.898880375415</v>
+        <v>1206.70567326583</v>
       </c>
       <c r="E271" s="3" t="inlineStr">
         <is>
@@ -10569,433 +10521,57 @@
       </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
-          <t>Q3-R02</t>
+          <t>Q3-R01</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="4" t="inlineStr">
         <is>
-          <t>Q2-025</t>
+          <t>Q2-026</t>
         </is>
       </c>
       <c r="B272" s="4" t="inlineStr">
         <is>
-          <t>leg2:descent</t>
+          <t>leg2:cruise</t>
         </is>
       </c>
       <c r="C272" s="4" t="n">
-        <v>3260.898880375415</v>
+        <v>1206.70567326583</v>
       </c>
       <c r="D272" s="4" t="n">
-        <v>3303.312063969165</v>
+        <v>1469.342128960893</v>
       </c>
       <c r="E272" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F272" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F272" s="3" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
         <is>
-          <t>Q2-025</t>
+          <t>Q2-026</t>
         </is>
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>S013:handover</t>
+          <t>leg2:descent</t>
         </is>
       </c>
       <c r="C273" s="4" t="n">
-        <v>3303.312063969165</v>
+        <v>1469.342128960893</v>
       </c>
       <c r="D273" s="4" t="n">
-        <v>3519.312063969165</v>
+        <v>1623.051398980424</v>
       </c>
       <c r="E273" s="3" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F273" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="4" t="inlineStr">
-        <is>
-          <t>Q2-025</t>
-        </is>
-      </c>
-      <c r="B274" s="4" t="inlineStr">
-        <is>
-          <t>leg3:climb</t>
-        </is>
-      </c>
-      <c r="C274" s="4" t="n">
-        <v>3519.312063969165</v>
-      </c>
-      <c r="D274" s="4" t="n">
-        <v>3538.304793461352</v>
-      </c>
-      <c r="E274" s="3" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F274" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="4" t="inlineStr">
-        <is>
-          <t>Q2-025</t>
-        </is>
-      </c>
-      <c r="B275" s="4" t="inlineStr">
-        <is>
-          <t>leg3:cruise</t>
-        </is>
-      </c>
-      <c r="C275" s="4" t="n">
-        <v>3538.304793461352</v>
-      </c>
-      <c r="D275" s="4" t="n">
-        <v>3594.149</v>
-      </c>
-      <c r="E275" s="3" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F275" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R02</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" s="4" t="inlineStr">
-        <is>
-          <t>Q2-025</t>
-        </is>
-      </c>
-      <c r="B276" s="4" t="inlineStr">
-        <is>
-          <t>leg3:cruise</t>
-        </is>
-      </c>
-      <c r="C276" s="4" t="n">
-        <v>3594.149</v>
-      </c>
-      <c r="D276" s="4" t="n">
-        <v>3598.358200799157</v>
-      </c>
-      <c r="E276" s="3" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F276" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R03</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" s="4" t="inlineStr">
-        <is>
-          <t>Q2-025</t>
-        </is>
-      </c>
-      <c r="B277" s="4" t="inlineStr">
-        <is>
-          <t>leg3:cruise</t>
-        </is>
-      </c>
-      <c r="C277" s="4" t="n">
-        <v>3598.358200799157</v>
-      </c>
-      <c r="D277" s="4" t="n">
-        <v>3861.587618610053</v>
-      </c>
-      <c r="E277" s="3" t="inlineStr">
-        <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F277" s="3" t="n"/>
-    </row>
-    <row r="278">
-      <c r="A278" s="4" t="inlineStr">
-        <is>
-          <t>Q2-025</t>
-        </is>
-      </c>
-      <c r="B278" s="4" t="inlineStr">
-        <is>
-          <t>leg3:descent</t>
-        </is>
-      </c>
-      <c r="C278" s="4" t="n">
-        <v>3861.587618610053</v>
-      </c>
-      <c r="D278" s="4" t="n">
-        <v>3997.328530475288</v>
-      </c>
-      <c r="E278" s="3" t="inlineStr">
-        <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F278" s="3" t="n"/>
-    </row>
-    <row r="279">
-      <c r="A279" s="4" t="inlineStr">
-        <is>
-          <t>Q2-026</t>
-        </is>
-      </c>
-      <c r="B279" s="4" t="inlineStr">
-        <is>
-          <t>leg1:climb</t>
-        </is>
-      </c>
-      <c r="C279" s="4" t="n">
-        <v>3356.099</v>
-      </c>
-      <c r="D279" s="4" t="n">
-        <v>3446.278722086589</v>
-      </c>
-      <c r="E279" s="3" t="inlineStr">
-        <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F279" s="3" t="n"/>
-    </row>
-    <row r="280">
-      <c r="A280" s="4" t="inlineStr">
-        <is>
-          <t>Q2-026</t>
-        </is>
-      </c>
-      <c r="B280" s="4" t="inlineStr">
-        <is>
-          <t>leg1:cruise</t>
-        </is>
-      </c>
-      <c r="C280" s="4" t="n">
-        <v>3446.278722086589</v>
-      </c>
-      <c r="D280" s="4" t="n">
-        <v>3818.643403304101</v>
-      </c>
-      <c r="E280" s="3" t="inlineStr">
-        <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F280" s="3" t="n"/>
-    </row>
-    <row r="281">
-      <c r="A281" s="4" t="inlineStr">
-        <is>
-          <t>Q2-026</t>
-        </is>
-      </c>
-      <c r="B281" s="4" t="inlineStr">
-        <is>
-          <t>leg1:cruise</t>
-        </is>
-      </c>
-      <c r="C281" s="4" t="n">
-        <v>3818.643403304101</v>
-      </c>
-      <c r="D281" s="4" t="n">
-        <v>3960.5918186944</v>
-      </c>
-      <c r="E281" s="3" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F281" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R03</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" s="4" t="inlineStr">
-        <is>
-          <t>Q2-026</t>
-        </is>
-      </c>
-      <c r="B282" s="4" t="inlineStr">
-        <is>
-          <t>leg1:descent</t>
-        </is>
-      </c>
-      <c r="C282" s="4" t="n">
-        <v>3960.5918186944</v>
-      </c>
-      <c r="D282" s="4" t="n">
-        <v>4028.567485198306</v>
-      </c>
-      <c r="E282" s="3" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F282" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R03</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" s="4" t="inlineStr">
-        <is>
-          <t>Q2-026</t>
-        </is>
-      </c>
-      <c r="B283" s="4" t="inlineStr">
-        <is>
-          <t>S004:handover</t>
-        </is>
-      </c>
-      <c r="C283" s="4" t="n">
-        <v>4028.567485198306</v>
-      </c>
-      <c r="D283" s="4" t="n">
-        <v>4208.567485198306</v>
-      </c>
-      <c r="E283" s="3" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F283" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R03</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" s="4" t="inlineStr">
-        <is>
-          <t>Q2-026</t>
-        </is>
-      </c>
-      <c r="B284" s="4" t="inlineStr">
-        <is>
-          <t>leg2:climb</t>
-        </is>
-      </c>
-      <c r="C284" s="4" t="n">
-        <v>4208.567485198306</v>
-      </c>
-      <c r="D284" s="4" t="n">
-        <v>4265.213873951561</v>
-      </c>
-      <c r="E284" s="3" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F284" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R03</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" s="4" t="inlineStr">
-        <is>
-          <t>Q2-026</t>
-        </is>
-      </c>
-      <c r="B285" s="4" t="inlineStr">
-        <is>
-          <t>leg2:cruise</t>
-        </is>
-      </c>
-      <c r="C285" s="4" t="n">
-        <v>4265.213873951561</v>
-      </c>
-      <c r="D285" s="4" t="n">
-        <v>4407.162289341861</v>
-      </c>
-      <c r="E285" s="3" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F285" s="3" t="inlineStr">
-        <is>
-          <t>Q3-R03</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" s="4" t="inlineStr">
-        <is>
-          <t>Q2-026</t>
-        </is>
-      </c>
-      <c r="B286" s="4" t="inlineStr">
-        <is>
-          <t>leg2:cruise</t>
-        </is>
-      </c>
-      <c r="C286" s="4" t="n">
-        <v>4407.162289341861</v>
-      </c>
-      <c r="D286" s="4" t="n">
-        <v>4779.526970559373</v>
-      </c>
-      <c r="E286" s="3" t="inlineStr">
-        <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F286" s="3" t="n"/>
-    </row>
-    <row r="287">
-      <c r="A287" s="4" t="inlineStr">
-        <is>
-          <t>Q2-026</t>
-        </is>
-      </c>
-      <c r="B287" s="4" t="inlineStr">
-        <is>
-          <t>leg2:descent</t>
-        </is>
-      </c>
-      <c r="C287" s="4" t="n">
-        <v>4779.526970559373</v>
-      </c>
-      <c r="D287" s="4" t="n">
-        <v>4887.742637063279</v>
-      </c>
-      <c r="E287" s="3" t="inlineStr">
-        <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F287" s="3" t="n"/>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F273" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
